--- a/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
+++ b/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://intelfon-my.sharepoint.com/personal/lngonzalez_red_com_sv/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Gonzalez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCF0CECC-D271-4BC2-A88A-310D3C47A8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C6B073-D9B6-4D15-8F5E-B776CFF27F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="21840" windowHeight="13140" firstSheet="1" activeTab="3" xr2:uid="{AE14704C-24AB-4D26-A00D-6B82B88C2662}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALDOS POR CUENTA" sheetId="3" r:id="rId1"/>
@@ -18,18 +18,8 @@
     <sheet name="REPORTE CREDITOS DIARIOS" sheetId="4" r:id="rId3"/>
     <sheet name="TABLERO CREDITOS" sheetId="5" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ESTADOS CONSOLIDADOS'!$A$1:$H$184</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'REPORTE CREDITOS DIARIOS'!$A$4:$K$23</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,17 +27,22 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="332">
+  <si>
+    <t>SALDOS INICIALES Y FINALES POR CUENTA</t>
+  </si>
+  <si>
+    <t>Valores tomados del primer y último movimiento registrado de los estados de cuenta en bancos.</t>
+  </si>
   <si>
     <t>Banco</t>
   </si>
@@ -55,6 +50,51 @@
     <t>Cuenta</t>
   </si>
   <si>
+    <t xml:space="preserve">Saldo inicial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo final </t>
+  </si>
+  <si>
+    <t>AGRÍCOLA</t>
+  </si>
+  <si>
+    <t>9596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUSCATLÁN </t>
+  </si>
+  <si>
+    <t>2509</t>
+  </si>
+  <si>
+    <t>4978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAC </t>
+  </si>
+  <si>
+    <t>0386</t>
+  </si>
+  <si>
+    <t>6715</t>
+  </si>
+  <si>
+    <t>PROMERICA</t>
+  </si>
+  <si>
+    <t>0049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAVIVIENDA </t>
+  </si>
+  <si>
+    <t>8202</t>
+  </si>
+  <si>
+    <t>1962</t>
+  </si>
+  <si>
     <t>Fecha Transacción</t>
   </si>
   <si>
@@ -76,9 +116,6 @@
     <t>BANCO AGRÍCOLA</t>
   </si>
   <si>
-    <t>9596</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -253,9 +290,6 @@
     <t>BANCO CUSCATLÁN</t>
   </si>
   <si>
-    <t>2509</t>
-  </si>
-  <si>
     <t>5972</t>
   </si>
   <si>
@@ -301,9 +335,6 @@
     <t>789692036</t>
   </si>
   <si>
-    <t>4978</t>
-  </si>
-  <si>
     <t>720107225</t>
   </si>
   <si>
@@ -400,9 +431,6 @@
     <t>BAC</t>
   </si>
   <si>
-    <t>0386</t>
-  </si>
-  <si>
     <t>189080846</t>
   </si>
   <si>
@@ -541,9 +569,6 @@
     <t>BELRED (-180826</t>
   </si>
   <si>
-    <t>6715</t>
-  </si>
-  <si>
     <t>912801313</t>
   </si>
   <si>
@@ -706,12 +731,6 @@
     <t>TEF DE:OCEANICA ESCUELA DE BUC</t>
   </si>
   <si>
-    <t>PROMERICA</t>
-  </si>
-  <si>
-    <t>0049</t>
-  </si>
-  <si>
     <t>Transferencia por cobro de servicios</t>
   </si>
   <si>
@@ -745,9 +764,6 @@
     <t>DAVIVIENDA</t>
   </si>
   <si>
-    <t>8202</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
@@ -868,9 +884,6 @@
     <t>WEB Transf a RUDY SACA</t>
   </si>
   <si>
-    <t>1962</t>
-  </si>
-  <si>
     <t>RETENCION IMPUESTO029601075000</t>
   </si>
   <si>
@@ -883,30 +896,6 @@
     <t>Pgo.interes.Dep.Plzo 078300</t>
   </si>
   <si>
-    <t>SALDOS INICIALES Y FINALES POR CUENTA</t>
-  </si>
-  <si>
-    <t>Valores tomados del primer y último movimiento registrado de los estados de cuenta en bancos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo inicial </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo final </t>
-  </si>
-  <si>
-    <t>AGRÍCOLA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUSCATLÁN </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BAC </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DAVIVIENDA </t>
-  </si>
-  <si>
     <t>RESUMEN DIARIO DE CRÉDITOS / ABONOS</t>
   </si>
   <si>
@@ -1036,30 +1025,32 @@
     <t>19/08</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
     <t>Nota: el reporte suma únicamente los valores existentes en Crédito / Abono / Valor +. Los movimientos originales permanecen sin cambios.</t>
+  </si>
+  <si>
+    <t>SALDO DISPONIBLE</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="0000"/>
-    <numFmt numFmtId="167" formatCode="\$#,##0.00;[Red]\-\$#,##0.00"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0000"/>
+    <numFmt numFmtId="168" formatCode="\$#,##0.00;[Red]\-\$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1141,8 +1132,28 @@
       <color rgb="FF203040"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF17365D"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF008080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="2" tint="-0.749992370372631"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1199,8 +1210,19 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1208,13 +1230,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF70AD47"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF70AD47"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1228,21 +1261,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1252,8 +1278,62 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="15" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1264,73 +1344,40 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="8" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="1" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="11" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Moneda 2" xfId="2" xr:uid="{0169ABB0-90A7-4E1D-8580-7AEADB7496D9}"/>
+    <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{43A31A1C-B7B0-4086-966B-0C915EBD7E65}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1365,11 +1412,8 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
             <a:r>
-              <a:rPr lang="es-SV"/>
+              <a:rPr lang="es-GT"/>
               <a:t>Evolución del crédito seleccionado</a:t>
             </a:r>
           </a:p>
@@ -1475,7 +1519,7 @@
             <c:numRef>
               <c:f>'TABLERO CREDITOS'!$B$15:$B$33</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;[Red]\-\$#,##0.00</c:formatCode>
+                <c:formatCode>\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>9716.2900000000009</c:v>
@@ -1540,7 +1584,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1B8E-4900-8BC9-CAD3E4F1EA54}"/>
+              <c16:uniqueId val="{00000000-6594-47E3-8145-010E8EFD41FC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1569,11 +1613,8 @@
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-SV"/>
+                  <a:rPr lang="es-GT"/>
                   <a:t>Fecha</a:t>
                 </a:r>
               </a:p>
@@ -1598,18 +1639,14 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
         <c:title>
           <c:tx>
             <c:rich>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-SV"/>
+                  <a:rPr lang="es-GT"/>
                   <a:t>Créditos</a:t>
                 </a:r>
               </a:p>
@@ -1617,7 +1654,7 @@
           </c:tx>
           <c:overlay val="1"/>
         </c:title>
-        <c:numFmt formatCode="\$#,##0.00;[Red]\-\$#,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1630,18 +1667,18 @@
       <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:txPr>
-        <a:bodyPr/>
+        <a:bodyPr anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr rtl="0">
             <a:defRPr/>
           </a:pPr>
-          <a:endParaRPr lang="es-SV"/>
+          <a:endParaRPr lang="es-GT"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
+    <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
@@ -1672,11 +1709,8 @@
           <a:bodyPr/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
             <a:r>
-              <a:rPr lang="es-SV"/>
+              <a:rPr lang="es-GT"/>
               <a:t>Créditos por cuenta en el rango</a:t>
             </a:r>
           </a:p>
@@ -1747,7 +1781,7 @@
             <c:numRef>
               <c:f>'TABLERO CREDITOS'!$H$15:$H$22</c:f>
               <c:numCache>
-                <c:formatCode>\$#,##0.00;[Red]\-\$#,##0.00</c:formatCode>
+                <c:formatCode>\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>24450.060000000005</c:v>
@@ -1778,7 +1812,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F630-458C-8ECC-3462647860FA}"/>
+              <c16:uniqueId val="{00000000-92AC-41A0-8F27-E22BB8285E16}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1810,7 +1844,7 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="100"/>
@@ -1819,8 +1853,7 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:numFmt formatCode="\$#,##0.00;[Red]\-\$#,##0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1834,7 +1867,7 @@
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
+    <c:dispBlanksAs val="zero"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:printSettings>
@@ -1857,16 +1890,14 @@
     <xdr:ext cx="5400000" cy="2700000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="2" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91634358-C168-4655-B5F1-094423A3AE81}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1890,16 +1921,14 @@
     <xdr:ext cx="5400000" cy="2700000"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="3" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1467EDF6-B27D-4E86-919D-A5A20741F55B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -1916,730 +1945,13 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="CUENTAS"/>
-      <sheetName val="ESTADOS CONSOLIDADOS"/>
-      <sheetName val="SALDOS POR CUENTA"/>
-      <sheetName val="REPORTE CREDITOS DIARIOS"/>
-      <sheetName val="REPORTE CREDITOS DIARIOS (2)"/>
-      <sheetName val="TABLERO CREDITOS"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4">
-        <row r="4">
-          <cell r="B4" t="str">
-            <v>9596</v>
-          </cell>
-          <cell r="C4" t="str">
-            <v>2509</v>
-          </cell>
-          <cell r="D4" t="str">
-            <v>4978</v>
-          </cell>
-          <cell r="E4" t="str">
-            <v>0386</v>
-          </cell>
-          <cell r="F4" t="str">
-            <v>6715</v>
-          </cell>
-          <cell r="G4" t="str">
-            <v>0049</v>
-          </cell>
-          <cell r="H4" t="str">
-            <v>8202</v>
-          </cell>
-          <cell r="I4" t="str">
-            <v>1962</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>46235</v>
-          </cell>
-          <cell r="B5">
-            <v>124.3</v>
-          </cell>
-          <cell r="D5">
-            <v>176.16</v>
-          </cell>
-          <cell r="E5">
-            <v>1015.83</v>
-          </cell>
-          <cell r="F5">
-            <v>8400</v>
-          </cell>
-          <cell r="J5">
-            <v>9716.2900000000009</v>
-          </cell>
-          <cell r="K5">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>46236</v>
-          </cell>
-          <cell r="J6">
-            <v>0</v>
-          </cell>
-          <cell r="K6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>46237</v>
-          </cell>
-          <cell r="B7">
-            <v>333.35</v>
-          </cell>
-          <cell r="D7">
-            <v>508.93</v>
-          </cell>
-          <cell r="F7">
-            <v>940.8</v>
-          </cell>
-          <cell r="G7">
-            <v>560.48</v>
-          </cell>
-          <cell r="J7">
-            <v>2343.56</v>
-          </cell>
-          <cell r="K7">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>46238</v>
-          </cell>
-          <cell r="B8">
-            <v>1929.79</v>
-          </cell>
-          <cell r="C8">
-            <v>985.6</v>
-          </cell>
-          <cell r="D8">
-            <v>160</v>
-          </cell>
-          <cell r="E8">
-            <v>827.16</v>
-          </cell>
-          <cell r="F8">
-            <v>211.31</v>
-          </cell>
-          <cell r="G8">
-            <v>57.63</v>
-          </cell>
-          <cell r="H8">
-            <v>124.3</v>
-          </cell>
-          <cell r="J8">
-            <v>4295.79</v>
-          </cell>
-          <cell r="K8">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>46239</v>
-          </cell>
-          <cell r="B9">
-            <v>197.75</v>
-          </cell>
-          <cell r="D9">
-            <v>100</v>
-          </cell>
-          <cell r="E9">
-            <v>45.2</v>
-          </cell>
-          <cell r="F9">
-            <v>824.9</v>
-          </cell>
-          <cell r="H9">
-            <v>335.61</v>
-          </cell>
-          <cell r="J9">
-            <v>1503.46</v>
-          </cell>
-          <cell r="K9">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>46240</v>
-          </cell>
-          <cell r="B10">
-            <v>622.82000000000005</v>
-          </cell>
-          <cell r="J10">
-            <v>622.82000000000005</v>
-          </cell>
-          <cell r="K10">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>46241</v>
-          </cell>
-          <cell r="B11">
-            <v>1115.8800000000001</v>
-          </cell>
-          <cell r="C11">
-            <v>67.8</v>
-          </cell>
-          <cell r="D11">
-            <v>461.98</v>
-          </cell>
-          <cell r="E11">
-            <v>1021.92</v>
-          </cell>
-          <cell r="G11">
-            <v>76.84</v>
-          </cell>
-          <cell r="I11">
-            <v>22.02</v>
-          </cell>
-          <cell r="J11">
-            <v>2766.44</v>
-          </cell>
-          <cell r="K11">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>46242</v>
-          </cell>
-          <cell r="E12">
-            <v>814.73</v>
-          </cell>
-          <cell r="J12">
-            <v>814.73</v>
-          </cell>
-          <cell r="K12">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>46243</v>
-          </cell>
-          <cell r="J13">
-            <v>0</v>
-          </cell>
-          <cell r="K13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>46244</v>
-          </cell>
-          <cell r="B14">
-            <v>716.42</v>
-          </cell>
-          <cell r="C14">
-            <v>113.14</v>
-          </cell>
-          <cell r="D14">
-            <v>267.26</v>
-          </cell>
-          <cell r="F14">
-            <v>911.91</v>
-          </cell>
-          <cell r="G14">
-            <v>554.83000000000004</v>
-          </cell>
-          <cell r="H14">
-            <v>192.1</v>
-          </cell>
-          <cell r="I14">
-            <v>79.89</v>
-          </cell>
-          <cell r="J14">
-            <v>2835.55</v>
-          </cell>
-          <cell r="K14">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>46245</v>
-          </cell>
-          <cell r="B15">
-            <v>904</v>
-          </cell>
-          <cell r="C15">
-            <v>372.9</v>
-          </cell>
-          <cell r="D15">
-            <v>604.79999999999995</v>
-          </cell>
-          <cell r="E15">
-            <v>0</v>
-          </cell>
-          <cell r="F15">
-            <v>225.25</v>
-          </cell>
-          <cell r="G15">
-            <v>552.16</v>
-          </cell>
-          <cell r="H15">
-            <v>30319</v>
-          </cell>
-          <cell r="J15">
-            <v>32978.11</v>
-          </cell>
-          <cell r="K15">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>46246</v>
-          </cell>
-          <cell r="B16">
-            <v>6110.3</v>
-          </cell>
-          <cell r="D16">
-            <v>729.98</v>
-          </cell>
-          <cell r="E16">
-            <v>640.59</v>
-          </cell>
-          <cell r="F16">
-            <v>281.29000000000002</v>
-          </cell>
-          <cell r="G16">
-            <v>56.5</v>
-          </cell>
-          <cell r="H16">
-            <v>544.59</v>
-          </cell>
-          <cell r="J16">
-            <v>8363.25</v>
-          </cell>
-          <cell r="K16">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>46247</v>
-          </cell>
-          <cell r="B17">
-            <v>604.86</v>
-          </cell>
-          <cell r="C17">
-            <v>1.38</v>
-          </cell>
-          <cell r="E17">
-            <v>169.3</v>
-          </cell>
-          <cell r="F17">
-            <v>564.08000000000004</v>
-          </cell>
-          <cell r="G17">
-            <v>1681.24</v>
-          </cell>
-          <cell r="H17">
-            <v>216.96</v>
-          </cell>
-          <cell r="J17">
-            <v>3237.82</v>
-          </cell>
-          <cell r="K17">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>46248</v>
-          </cell>
-          <cell r="B18">
-            <v>9077.44</v>
-          </cell>
-          <cell r="C18">
-            <v>66.67</v>
-          </cell>
-          <cell r="D18">
-            <v>25.99</v>
-          </cell>
-          <cell r="E18">
-            <v>1893.46</v>
-          </cell>
-          <cell r="F18">
-            <v>0</v>
-          </cell>
-          <cell r="G18">
-            <v>335.61</v>
-          </cell>
-          <cell r="H18">
-            <v>0</v>
-          </cell>
-          <cell r="J18">
-            <v>11399.17</v>
-          </cell>
-          <cell r="K18">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>46249</v>
-          </cell>
-          <cell r="D19">
-            <v>532.23</v>
-          </cell>
-          <cell r="E19">
-            <v>40.99</v>
-          </cell>
-          <cell r="F19">
-            <v>84.75</v>
-          </cell>
-          <cell r="H19">
-            <v>244.08</v>
-          </cell>
-          <cell r="J19">
-            <v>902.05</v>
-          </cell>
-          <cell r="K19">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>46250</v>
-          </cell>
-          <cell r="B20">
-            <v>282.5</v>
-          </cell>
-          <cell r="E20">
-            <v>237.34</v>
-          </cell>
-          <cell r="J20">
-            <v>519.84</v>
-          </cell>
-          <cell r="K20">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>46251</v>
-          </cell>
-          <cell r="B21">
-            <v>387.59</v>
-          </cell>
-          <cell r="C21">
-            <v>21.47</v>
-          </cell>
-          <cell r="D21">
-            <v>793.26</v>
-          </cell>
-          <cell r="F21">
-            <v>637.25</v>
-          </cell>
-          <cell r="G21">
-            <v>966.05</v>
-          </cell>
-          <cell r="H21">
-            <v>728.06</v>
-          </cell>
-          <cell r="J21">
-            <v>3533.68</v>
-          </cell>
-          <cell r="K21">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>46252</v>
-          </cell>
-          <cell r="B22">
-            <v>1671.29</v>
-          </cell>
-          <cell r="C22">
-            <v>6163.5</v>
-          </cell>
-          <cell r="D22">
-            <v>339</v>
-          </cell>
-          <cell r="E22">
-            <v>307.38</v>
-          </cell>
-          <cell r="G22">
-            <v>310.24</v>
-          </cell>
-          <cell r="J22">
-            <v>8791.41</v>
-          </cell>
-          <cell r="K22">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>46253</v>
-          </cell>
-          <cell r="B23">
-            <v>371.77</v>
-          </cell>
-          <cell r="D23">
-            <v>56.5</v>
-          </cell>
-          <cell r="E23">
-            <v>2093.02</v>
-          </cell>
-          <cell r="F23">
-            <v>5251.38</v>
-          </cell>
-          <cell r="G23">
-            <v>485.25</v>
-          </cell>
-          <cell r="J23">
-            <v>8257.92</v>
-          </cell>
-          <cell r="K23">
-            <v>5</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5">
-        <row r="14">
-          <cell r="B14" t="str">
-            <v>Crédito seleccionado</v>
-          </cell>
-          <cell r="H14" t="str">
-            <v>Crédito en rango</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>46235</v>
-          </cell>
-          <cell r="B15">
-            <v>9716.2900000000009</v>
-          </cell>
-          <cell r="G15" t="str">
-            <v>9596</v>
-          </cell>
-          <cell r="H15">
-            <v>24450.060000000005</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>46236</v>
-          </cell>
-          <cell r="B16">
-            <v>0</v>
-          </cell>
-          <cell r="G16" t="str">
-            <v>2509</v>
-          </cell>
-          <cell r="H16">
-            <v>7792.46</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>46237</v>
-          </cell>
-          <cell r="B17">
-            <v>2343.56</v>
-          </cell>
-          <cell r="G17" t="str">
-            <v>4978</v>
-          </cell>
-          <cell r="H17">
-            <v>4756.09</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>46238</v>
-          </cell>
-          <cell r="B18">
-            <v>4295.79</v>
-          </cell>
-          <cell r="G18" t="str">
-            <v>0386</v>
-          </cell>
-          <cell r="H18">
-            <v>9106.92</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>46239</v>
-          </cell>
-          <cell r="B19">
-            <v>1503.46</v>
-          </cell>
-          <cell r="G19" t="str">
-            <v>6715</v>
-          </cell>
-          <cell r="H19">
-            <v>18332.919999999998</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>46240</v>
-          </cell>
-          <cell r="B20">
-            <v>622.82000000000005</v>
-          </cell>
-          <cell r="G20" t="str">
-            <v>0049</v>
-          </cell>
-          <cell r="H20">
-            <v>5636.83</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>46241</v>
-          </cell>
-          <cell r="B21">
-            <v>2766.44</v>
-          </cell>
-          <cell r="G21" t="str">
-            <v>8202</v>
-          </cell>
-          <cell r="H21">
-            <v>32704.7</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>46242</v>
-          </cell>
-          <cell r="B22">
-            <v>814.73</v>
-          </cell>
-          <cell r="G22" t="str">
-            <v>1962</v>
-          </cell>
-          <cell r="H22">
-            <v>101.91</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>46243</v>
-          </cell>
-          <cell r="B23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>46244</v>
-          </cell>
-          <cell r="B24">
-            <v>2835.55</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>46245</v>
-          </cell>
-          <cell r="B25">
-            <v>32978.11</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>46246</v>
-          </cell>
-          <cell r="B26">
-            <v>8363.25</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>46247</v>
-          </cell>
-          <cell r="B27">
-            <v>3237.82</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>46248</v>
-          </cell>
-          <cell r="B28">
-            <v>11399.17</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>46249</v>
-          </cell>
-          <cell r="B29">
-            <v>902.05</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>46250</v>
-          </cell>
-          <cell r="B30">
-            <v>519.84</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>46251</v>
-          </cell>
-          <cell r="B31">
-            <v>3533.68</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>46252</v>
-          </cell>
-          <cell r="B32">
-            <v>8791.41</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>46253</v>
-          </cell>
-          <cell r="B33">
-            <v>8257.92</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2757062B-013C-488C-AF1D-157E38F20CFD}" name="SaldosPorCuenta" displayName="SaldosPorCuenta" ref="A4:D12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SaldosPorCuenta" displayName="SaldosPorCuenta" ref="A4:D12" totalsRowShown="0">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{180A2204-13F7-409E-AA17-2D6D99F93765}" name="Banco"/>
-    <tableColumn id="2" xr3:uid="{3B07CDE4-FC22-4C7E-B6D7-A794A12C8E5E}" name="Cuenta"/>
-    <tableColumn id="3" xr3:uid="{49419EEF-1000-4B9F-A30B-046F611019FC}" name="Saldo inicial "/>
-    <tableColumn id="4" xr3:uid="{72297D4E-D26E-45A6-BC9E-7CAB527D1072}" name="Saldo final "/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Banco"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cuenta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Saldo inicial "/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Saldo final "/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2688,108 +2000,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2801,23 +2019,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2827,23 +2045,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2851,26 +2069,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -2905,17 +2120,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -2932,164 +2147,159 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8B18D83-CCF8-4DB8-A883-15CFDFF268B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="8" customWidth="1"/>
-    <col min="3" max="4" width="27.42578125" style="8" customWidth="1"/>
-    <col min="5" max="16384" width="10.28515625" style="8"/>
+    <col min="1" max="1" width="27.44140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="8" customWidth="1"/>
+    <col min="3" max="4" width="27.44140625" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.1" customHeight="1">
-      <c r="A1" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="4" spans="1:4" ht="30" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="12" t="s">
+    <row r="1" spans="1:4" ht="20.85" customHeight="1">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+    </row>
+    <row r="2" spans="1:4" ht="22.35" customHeight="1">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+    </row>
+    <row r="4" spans="1:4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="12">
+        <v>76663.7</v>
+      </c>
+      <c r="D5" s="12">
+        <v>71075.34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="15">
-        <v>76663.7</v>
-      </c>
-      <c r="D5" s="15">
-        <v>71075.34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" s="15">
+      <c r="C6" s="12">
         <v>14148.75</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="12">
         <v>21941.21</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="15">
+    <row r="7" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="12">
         <v>33171.599999999999</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="12">
         <v>28319.18</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="15">
+    <row r="8" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="12">
         <v>9086.82</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="12">
         <v>6003.86</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="C9" s="15">
+    <row r="9" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="12">
         <v>80183.38</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="12">
         <v>81910.289999999994</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="13" t="s">
-        <v>219</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="C10" s="15">
+    <row r="10" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="12">
         <v>51799.49</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="12">
         <v>33700.51</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="C11" s="15">
+    <row r="11" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A11" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="12">
         <v>38443.89</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="12">
         <v>25869.5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="C12" s="15">
+    <row r="12" spans="1:4" ht="16.05" customHeight="1">
+      <c r="A12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="12">
         <v>31.71</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="12">
         <v>125.63</v>
       </c>
     </row>
@@ -3106,63 +2316,63 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C662DC65-B321-4FB2-9604-D446FCE99AB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H184"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="24" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" style="3" customWidth="1"/>
     <col min="5" max="5" width="40" style="3" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="30.85546875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="29.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="30.88671875" style="8" customWidth="1"/>
     <col min="8" max="8" width="40" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="10.28515625" style="3"/>
+    <col min="9" max="9" width="10.33203125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="10.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="33.950000000000003" customHeight="1">
+    <row r="1" spans="1:8" ht="27.15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2" s="5">
         <v>46235</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F2" s="6">
         <v>0</v>
@@ -3176,19 +2386,19 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" s="5">
         <v>46235</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F3" s="6">
         <v>0</v>
@@ -3202,19 +2412,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5">
         <v>46237</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F4" s="6">
         <v>0</v>
@@ -3228,19 +2438,19 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="5">
         <v>46238</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
@@ -3254,19 +2464,19 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="5">
         <v>46239</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
@@ -3280,19 +2490,19 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C7" s="5">
         <v>46240</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F7" s="6">
         <v>0</v>
@@ -3306,19 +2516,19 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5">
         <v>46240</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F8" s="6">
         <v>0</v>
@@ -3332,19 +2542,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5">
         <v>46241</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F9" s="6">
         <v>0</v>
@@ -3358,19 +2568,19 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C10" s="5">
         <v>46241</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F10" s="6">
         <v>0</v>
@@ -3384,19 +2594,19 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5">
         <v>46241</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
@@ -3410,19 +2620,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="5">
         <v>46244</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F12" s="6">
         <v>0</v>
@@ -3436,19 +2646,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C13" s="5">
         <v>46244</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F13" s="6">
         <v>0</v>
@@ -3462,19 +2672,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C14" s="5">
         <v>46245</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F14" s="6">
         <v>0</v>
@@ -3488,19 +2698,19 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C15" s="5">
         <v>46245</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F15" s="6">
         <v>30000</v>
@@ -3514,19 +2724,19 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C16" s="5">
         <v>46245</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="F16" s="6">
         <v>0</v>
@@ -3540,19 +2750,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="5">
         <v>46245</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F17" s="6">
         <v>0</v>
@@ -3566,19 +2776,19 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" s="5">
         <v>46246</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F18" s="6">
         <v>0</v>
@@ -3592,19 +2802,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" s="5">
         <v>46246</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="F19" s="6">
         <v>0</v>
@@ -3618,19 +2828,19 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20" s="5">
         <v>46246</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="F20" s="6">
         <v>0</v>
@@ -3644,19 +2854,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C21" s="5">
         <v>46246</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="F21" s="6">
         <v>0</v>
@@ -3670,19 +2880,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22" s="5">
         <v>46246</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F22" s="6">
         <v>0</v>
@@ -3696,19 +2906,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" s="5">
         <v>46246</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="F23" s="6">
         <v>0</v>
@@ -3722,19 +2932,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" s="5">
         <v>46247</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F24" s="6">
         <v>0</v>
@@ -3748,19 +2958,19 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5">
         <v>46247</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F25" s="6">
         <v>0</v>
@@ -3774,19 +2984,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C26" s="5">
         <v>46247</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F26" s="6">
         <v>0</v>
@@ -3800,19 +3010,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C27" s="5">
         <v>46248</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F27" s="6">
         <v>0</v>
@@ -3826,19 +3036,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28" s="5">
         <v>46248</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="F28" s="6">
         <v>0</v>
@@ -3852,19 +3062,19 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" s="5">
         <v>46248</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F29" s="6">
         <v>0</v>
@@ -3878,19 +3088,19 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30" s="5">
         <v>46248</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F30" s="6">
         <v>0</v>
@@ -3904,19 +3114,19 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31" s="5">
         <v>46248</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F31" s="6">
         <v>0</v>
@@ -3930,19 +3140,19 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C32" s="5">
         <v>46248</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F32" s="6">
         <v>0</v>
@@ -3956,19 +3166,19 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C33" s="5">
         <v>46248</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="F33" s="6">
         <v>0</v>
@@ -3982,19 +3192,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C34" s="5">
         <v>46248</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="F34" s="6">
         <v>0</v>
@@ -4008,19 +3218,19 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35" s="5">
         <v>46248</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="F35" s="6">
         <v>0</v>
@@ -4034,19 +3244,19 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" s="5">
         <v>46250</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F36" s="6">
         <v>0</v>
@@ -4060,19 +3270,19 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" s="5">
         <v>46251</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F37" s="6">
         <v>0</v>
@@ -4086,19 +3296,19 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" s="5">
         <v>46252</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F38" s="6">
         <v>0</v>
@@ -4112,19 +3322,19 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39" s="5">
         <v>46252</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F39" s="6">
         <v>0</v>
@@ -4138,19 +3348,19 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C40" s="5">
         <v>46252</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="F40" s="6">
         <v>0</v>
@@ -4164,19 +3374,19 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C41" s="5">
         <v>46252</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F41" s="6">
         <v>0</v>
@@ -4190,19 +3400,19 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C42" s="5">
         <v>46252</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="F42" s="6">
         <v>0</v>
@@ -4216,19 +3426,19 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="4" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C43" s="5">
         <v>46253</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="F43" s="6">
         <v>0</v>
@@ -4242,19 +3452,19 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C44" s="5">
         <v>46237</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F44" s="6">
         <v>669.5</v>
@@ -4268,19 +3478,19 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C45" s="5">
         <v>46238</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F45" s="6">
         <v>0</v>
@@ -4294,19 +3504,19 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C46" s="5">
         <v>46241</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F46" s="6">
         <v>0</v>
@@ -4320,19 +3530,19 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C47" s="5">
         <v>46244</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F47" s="6">
         <v>0</v>
@@ -4346,19 +3556,19 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C48" s="5">
         <v>46245</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F48" s="6">
         <v>0</v>
@@ -4372,19 +3582,19 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="F49" s="6">
         <v>0</v>
@@ -4398,19 +3608,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C50" s="5">
         <v>46248</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F50" s="6">
         <v>0</v>
@@ -4424,19 +3634,19 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C51" s="5">
         <v>46251</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="F51" s="6">
         <v>0</v>
@@ -4450,19 +3660,19 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C52" s="5">
         <v>46252</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="F52" s="6">
         <v>0</v>
@@ -4476,19 +3686,19 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C53" s="5">
         <v>46235</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F53" s="6">
         <v>0</v>
@@ -4502,19 +3712,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C54" s="5">
         <v>46235</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F54" s="6">
         <v>1691.79</v>
@@ -4528,19 +3738,19 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C55" s="5">
         <v>46237</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F55" s="6">
         <v>0</v>
@@ -4554,19 +3764,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C56" s="5">
         <v>46237</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F56" s="6">
         <v>454.71</v>
@@ -4580,19 +3790,19 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C57" s="5">
         <v>46237</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F57" s="6">
         <v>0</v>
@@ -4606,19 +3816,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C58" s="5">
         <v>46238</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F58" s="6">
         <v>3337.2</v>
@@ -4632,19 +3842,19 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C59" s="5">
         <v>46238</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="F59" s="6">
         <v>3337.2</v>
@@ -4658,19 +3868,19 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C60" s="5">
         <v>46238</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F60" s="6">
         <v>0</v>
@@ -4684,19 +3894,19 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C61" s="5">
         <v>46239</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F61" s="6">
         <v>0</v>
@@ -4710,19 +3920,19 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C62" s="5">
         <v>46241</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>100</v>
-      </c>
-      <c r="E62" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="F62" s="6">
         <v>0</v>
@@ -4736,19 +3946,19 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C63" s="5">
         <v>46241</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F63" s="6">
         <v>0</v>
@@ -4762,19 +3972,19 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C64" s="5">
         <v>46244</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F64" s="6">
         <v>0</v>
@@ -4788,19 +3998,19 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C65" s="5">
         <v>46244</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F65" s="6">
         <v>0</v>
@@ -4814,19 +4024,19 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C66" s="5">
         <v>46245</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="F66" s="6">
         <v>0</v>
@@ -4840,19 +4050,19 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C67" s="5">
         <v>46246</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F67" s="6">
         <v>0</v>
@@ -4866,19 +4076,19 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C68" s="5">
         <v>46247</v>
       </c>
       <c r="D68" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E68" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>92</v>
       </c>
       <c r="F68" s="6">
         <v>457.77</v>
@@ -4892,19 +4102,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C69" s="5">
         <v>46248</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F69" s="6">
         <v>0</v>
@@ -4918,19 +4128,19 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C70" s="5">
         <v>46249</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F70" s="6">
         <v>0</v>
@@ -4944,19 +4154,19 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C71" s="5">
         <v>46249</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F71" s="6">
         <v>0</v>
@@ -4970,19 +4180,19 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C72" s="5">
         <v>46251</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F72" s="6">
         <v>0</v>
@@ -4996,19 +4206,19 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C73" s="5">
         <v>46251</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="F73" s="6">
         <v>153.68</v>
@@ -5022,19 +4232,19 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C74" s="5">
         <v>46251</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F74" s="6">
         <v>0</v>
@@ -5048,19 +4258,19 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C75" s="5">
         <v>46251</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="F75" s="6">
         <v>0</v>
@@ -5074,19 +4284,19 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5">
         <v>46252</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F76" s="6">
         <v>0</v>
@@ -5100,19 +4310,19 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="4" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="C77" s="5">
         <v>46253</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F77" s="6">
         <v>0</v>
@@ -5126,19 +4336,19 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C78" s="5">
         <v>46235</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="F78" s="6">
         <v>0</v>
@@ -5152,19 +4362,19 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C79" s="5">
         <v>46235</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F79" s="6">
         <v>0</v>
@@ -5178,19 +4388,19 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C80" s="5">
         <v>46238</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="F80" s="6">
         <v>0</v>
@@ -5204,19 +4414,19 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C81" s="5">
         <v>46239</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="F81" s="6">
         <v>0</v>
@@ -5230,19 +4440,19 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C82" s="5">
         <v>46241</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="F82" s="6">
         <v>0</v>
@@ -5256,19 +4466,19 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C83" s="5">
         <v>46241</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="F83" s="6">
         <v>0</v>
@@ -5282,19 +4492,19 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C84" s="5">
         <v>46242</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="F84" s="6">
         <v>0</v>
@@ -5308,19 +4518,19 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C85" s="5">
         <v>46245</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F85" s="6">
         <v>10622.25</v>
@@ -5334,19 +4544,19 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C86" s="5">
         <v>46246</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="F86" s="6">
         <v>0</v>
@@ -5360,19 +4570,19 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C87" s="5">
         <v>46246</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="F87" s="6">
         <v>0</v>
@@ -5386,19 +4596,19 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C88" s="5">
         <v>46246</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F88" s="6">
         <v>391.97</v>
@@ -5412,19 +4622,19 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C89" s="5">
         <v>46247</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="F89" s="6">
         <v>0</v>
@@ -5438,19 +4648,19 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C90" s="5">
         <v>46247</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="F90" s="6">
         <v>0</v>
@@ -5464,19 +4674,19 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C91" s="5">
         <v>46248</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F91" s="6">
         <v>0</v>
@@ -5490,19 +4700,19 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C92" s="5">
         <v>46248</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F92" s="6">
         <v>0</v>
@@ -5516,19 +4726,19 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C93" s="5">
         <v>46248</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F93" s="6">
         <v>565</v>
@@ -5542,19 +4752,19 @@
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C94" s="5">
         <v>46248</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F94" s="6">
         <v>0</v>
@@ -5568,19 +4778,19 @@
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C95" s="5">
         <v>46249</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F95" s="6">
         <v>0</v>
@@ -5594,19 +4804,19 @@
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C96" s="5">
         <v>46250</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F96" s="6">
         <v>0</v>
@@ -5620,19 +4830,19 @@
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C97" s="5">
         <v>46252</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F97" s="6">
         <v>228.76</v>
@@ -5646,19 +4856,19 @@
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C98" s="5">
         <v>46252</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F98" s="6">
         <v>0</v>
@@ -5672,19 +4882,19 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C99" s="5">
         <v>46253</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F99" s="6">
         <v>0</v>
@@ -5698,19 +4908,19 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>117</v>
+        <v>12</v>
       </c>
       <c r="C100" s="5">
         <v>46253</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F100" s="6">
         <v>0</v>
@@ -5724,19 +4934,19 @@
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C101" s="5">
         <v>46235</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="F101" s="6">
         <v>0</v>
@@ -5750,19 +4960,19 @@
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C102" s="5">
         <v>46237</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F102" s="6">
         <v>0</v>
@@ -5776,19 +4986,19 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C103" s="5">
         <v>46238</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="F103" s="6">
         <v>0</v>
@@ -5802,19 +5012,19 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C104" s="5">
         <v>46239</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F104" s="6">
         <v>0</v>
@@ -5828,19 +5038,19 @@
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C105" s="5">
         <v>46239</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="F105" s="6">
         <v>0</v>
@@ -5854,19 +5064,19 @@
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C106" s="5">
         <v>46244</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F106" s="6">
         <v>0</v>
@@ -5880,19 +5090,19 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C107" s="5">
         <v>46244</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F107" s="6">
         <v>0</v>
@@ -5906,19 +5116,19 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C108" s="5">
         <v>46244</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F108" s="6">
         <v>0</v>
@@ -5932,19 +5142,19 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C109" s="5">
         <v>46244</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="F109" s="6">
         <v>0</v>
@@ -5958,19 +5168,19 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C110" s="5">
         <v>46245</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F110" s="6">
         <v>0</v>
@@ -5984,19 +5194,19 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C111" s="5">
         <v>46245</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F111" s="6">
         <v>0</v>
@@ -6010,19 +5220,19 @@
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C112" s="5">
         <v>46246</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="F112" s="6">
         <v>0</v>
@@ -6036,19 +5246,19 @@
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C113" s="5">
         <v>46246</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F113" s="6">
         <v>0</v>
@@ -6062,19 +5272,19 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C114" s="5">
         <v>46247</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F114" s="6">
         <v>0</v>
@@ -6088,19 +5298,19 @@
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C115" s="5">
         <v>46247</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F115" s="6">
         <v>0</v>
@@ -6114,19 +5324,19 @@
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C116" s="5">
         <v>46247</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F116" s="6">
         <v>0</v>
@@ -6140,19 +5350,19 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C117" s="5">
         <v>46248</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="F117" s="6">
         <v>2470.77</v>
@@ -6166,19 +5376,19 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C118" s="5">
         <v>46248</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="F118" s="6">
         <v>651.86</v>
@@ -6192,19 +5402,19 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C119" s="5">
         <v>46249</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="F119" s="6">
         <v>0</v>
@@ -6218,19 +5428,19 @@
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C120" s="5">
         <v>46251</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="F120" s="6">
         <v>0</v>
@@ -6244,19 +5454,19 @@
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C121" s="5">
         <v>46251</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="F121" s="6">
         <v>0</v>
@@ -6270,19 +5480,19 @@
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C122" s="5">
         <v>46251</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="F122" s="6">
         <v>885.39</v>
@@ -6296,19 +5506,19 @@
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C123" s="5">
         <v>46251</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F123" s="6">
         <v>0</v>
@@ -6322,19 +5532,19 @@
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C124" s="5">
         <v>46253</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F124" s="6">
         <v>0</v>
@@ -6348,19 +5558,19 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C125" s="5">
         <v>46253</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F125" s="6">
         <v>4135.04</v>
@@ -6374,19 +5584,19 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C126" s="5">
         <v>46253</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F126" s="6">
         <v>62.95</v>
@@ -6400,19 +5610,19 @@
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C127" s="5">
         <v>46253</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F127" s="6">
         <v>0</v>
@@ -6426,19 +5636,19 @@
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="4" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="C128" s="5">
         <v>46253</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="F128" s="6">
         <v>0</v>
@@ -6452,10 +5662,10 @@
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C129" s="5">
         <v>46237.006354166668</v>
@@ -6464,7 +5674,7 @@
         <v>554582578</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F129" s="6">
         <v>0</v>
@@ -6478,10 +5688,10 @@
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C130" s="5">
         <v>46237.407800925917</v>
@@ -6490,7 +5700,7 @@
         <v>826478</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F130" s="6">
         <v>2373</v>
@@ -6504,10 +5714,10 @@
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C131" s="5">
         <v>46238.002337962957</v>
@@ -6516,7 +5726,7 @@
         <v>554961533</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F131" s="6">
         <v>0</v>
@@ -6530,10 +5740,10 @@
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C132" s="5">
         <v>46238.46429398148</v>
@@ -6542,7 +5752,7 @@
         <v>826479</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="F132" s="6">
         <v>81.36</v>
@@ -6556,10 +5766,10 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C133" s="5">
         <v>46241.000625000001</v>
@@ -6568,7 +5778,7 @@
         <v>556005146</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F133" s="6">
         <v>0</v>
@@ -6582,10 +5792,10 @@
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C134" s="5">
         <v>46241.54005787037</v>
@@ -6594,7 +5804,7 @@
         <v>826468</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F134" s="6">
         <v>384</v>
@@ -6608,10 +5818,10 @@
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C135" s="5">
         <v>46244.40084490741</v>
@@ -6620,7 +5830,7 @@
         <v>45935253</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F135" s="6">
         <v>0</v>
@@ -6634,10 +5844,10 @@
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C136" s="5">
         <v>46245.007407407407</v>
@@ -6646,7 +5856,7 @@
         <v>557403713</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F136" s="6">
         <v>0</v>
@@ -6660,10 +5870,10 @@
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C137" s="5">
         <v>46246.058935185189</v>
@@ -6672,7 +5882,7 @@
         <v>557765645</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F137" s="6">
         <v>0</v>
@@ -6686,10 +5896,10 @@
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C138" s="5">
         <v>46247.007164351853</v>
@@ -6698,7 +5908,7 @@
         <v>558124083</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F138" s="6">
         <v>0</v>
@@ -6712,10 +5922,10 @@
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C139" s="5">
         <v>46247.428495370368</v>
@@ -6724,7 +5934,7 @@
         <v>45935255</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F139" s="6">
         <v>0</v>
@@ -6738,10 +5948,10 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C140" s="5">
         <v>46247.430266203701</v>
@@ -6750,7 +5960,7 @@
         <v>45935256</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F140" s="6">
         <v>0</v>
@@ -6764,10 +5974,10 @@
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C141" s="5">
         <v>46248.006377314807</v>
@@ -6776,7 +5986,7 @@
         <v>558581183</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F141" s="6">
         <v>0</v>
@@ -6790,10 +6000,10 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C142" s="5">
         <v>46248.688101851847</v>
@@ -6802,7 +6012,7 @@
         <v>558471426</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="F142" s="6">
         <v>437.19</v>
@@ -6816,10 +6026,10 @@
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C143" s="5">
         <v>46248.733877314808</v>
@@ -6828,7 +6038,7 @@
         <v>558504544</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F143" s="6">
         <v>5277.98</v>
@@ -6842,10 +6052,10 @@
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C144" s="5">
         <v>46248.733877314808</v>
@@ -6854,7 +6064,7 @@
         <v>558504550</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="F144" s="6">
         <v>8769.2099999999991</v>
@@ -6868,10 +6078,10 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C145" s="5">
         <v>46248.733888888892</v>
@@ -6880,7 +6090,7 @@
         <v>558504558</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F145" s="6">
         <v>3766.21</v>
@@ -6894,10 +6104,10 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C146" s="5">
         <v>46251.595462962963</v>
@@ -6906,7 +6116,7 @@
         <v>45935257</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F146" s="6">
         <v>0</v>
@@ -6920,10 +6130,10 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C147" s="5">
         <v>46251.765034722222</v>
@@ -6932,7 +6142,7 @@
         <v>559793518</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F147" s="6">
         <v>276.58</v>
@@ -6946,10 +6156,10 @@
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C148" s="5">
         <v>46251.765057870369</v>
@@ -6958,7 +6168,7 @@
         <v>559793529</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F148" s="6">
         <v>363.45</v>
@@ -6972,10 +6182,10 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C149" s="5">
         <v>46251.765081018522</v>
@@ -6984,7 +6194,7 @@
         <v>559793534</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F149" s="6">
         <v>391.85</v>
@@ -6998,10 +6208,10 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C150" s="5">
         <v>46251.765115740738</v>
@@ -7010,7 +6220,7 @@
         <v>559793544</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F150" s="6">
         <v>1054.5</v>
@@ -7024,10 +6234,10 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C151" s="5">
         <v>46252.380648148152</v>
@@ -7036,7 +6246,7 @@
         <v>40518427</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F151" s="6">
         <v>0</v>
@@ -7050,10 +6260,10 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C152" s="5">
         <v>46252.382534722223</v>
@@ -7062,7 +6272,7 @@
         <v>40518426</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F152" s="6">
         <v>0</v>
@@ -7076,10 +6286,10 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C153" s="5">
         <v>46253.090370370373</v>
@@ -7088,7 +6298,7 @@
         <v>560650177</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F153" s="6">
         <v>0</v>
@@ -7102,10 +6312,10 @@
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C154" s="5">
         <v>46253.394594907397</v>
@@ -7114,7 +6324,7 @@
         <v>45935258</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F154" s="6">
         <v>0</v>
@@ -7128,10 +6338,10 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="4" t="s">
-        <v>219</v>
+        <v>14</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>220</v>
+        <v>15</v>
       </c>
       <c r="C155" s="5">
         <v>46253.395752314813</v>
@@ -7140,7 +6350,7 @@
         <v>45935260</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="F155" s="6">
         <v>0</v>
@@ -7154,19 +6364,19 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C156" s="5">
         <v>46238</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F156" s="6">
         <v>0</v>
@@ -7180,19 +6390,19 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C157" s="5">
         <v>46238</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F157" s="6">
         <v>13140.34</v>
@@ -7206,19 +6416,19 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C158" s="5">
         <v>46238</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F158" s="6">
         <v>2768.72</v>
@@ -7232,19 +6442,19 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C159" s="5">
         <v>46238</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F159" s="6">
         <v>2080.84</v>
@@ -7258,19 +6468,19 @@
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C160" s="5">
         <v>46239</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="F160" s="6">
         <v>0</v>
@@ -7284,19 +6494,19 @@
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C161" s="5">
         <v>46244</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F161" s="6">
         <v>0</v>
@@ -7310,19 +6520,19 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="4" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C162" s="5">
         <v>46244</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="F162" s="6">
         <v>272.74</v>
@@ -7336,19 +6546,19 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C163" s="7">
         <v>46245</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="F163" s="6">
         <v>0</v>
@@ -7362,19 +6572,19 @@
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C164" s="7">
         <v>46245</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F164" s="6">
         <v>0</v>
@@ -7388,19 +6598,19 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C165" s="7">
         <v>46246</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F165" s="6">
         <v>0</v>
@@ -7414,19 +6624,19 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C166" s="7">
         <v>46246</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F166" s="6">
         <v>0</v>
@@ -7440,19 +6650,19 @@
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C167" s="7">
         <v>46246</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F167" s="6">
         <v>0</v>
@@ -7466,19 +6676,19 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C168" s="7">
         <v>46246</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F168" s="6">
         <v>0</v>
@@ -7492,19 +6702,19 @@
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C169" s="7">
         <v>46247</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="F169" s="6">
         <v>0</v>
@@ -7518,19 +6728,19 @@
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C170" s="7">
         <v>46247</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="F170" s="6">
         <v>0</v>
@@ -7544,19 +6754,19 @@
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C171" s="7">
         <v>46248</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="F171" s="6">
         <v>4300</v>
@@ -7570,19 +6780,19 @@
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C172" s="7">
         <v>46248</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F172" s="6">
         <v>18520.400000000001</v>
@@ -7596,19 +6806,19 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C173" s="7">
         <v>46248</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="F173" s="6">
         <v>320</v>
@@ -7622,19 +6832,19 @@
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C174" s="7">
         <v>46248</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E174" s="8" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F174" s="6">
         <v>2791.54</v>
@@ -7648,19 +6858,19 @@
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C175" s="7">
         <v>46248</v>
       </c>
       <c r="D175" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E175" s="8" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="F175" s="6">
         <v>183.96</v>
@@ -7674,19 +6884,19 @@
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C176" s="7">
         <v>46248</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="E176" s="8" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F176" s="6">
         <v>81</v>
@@ -7700,19 +6910,19 @@
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C177" s="7">
         <v>46249</v>
       </c>
       <c r="D177" s="8" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="E177" s="8" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F177" s="6">
         <v>0</v>
@@ -7726,19 +6936,19 @@
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C178" s="7">
         <v>46251</v>
       </c>
       <c r="D178" s="8" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E178" s="8" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F178" s="6">
         <v>0</v>
@@ -7752,19 +6962,19 @@
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C179" s="7">
         <v>46251</v>
       </c>
       <c r="D179" s="8" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="E179" s="8" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F179" s="6">
         <v>0</v>
@@ -7778,19 +6988,19 @@
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>232</v>
+        <v>17</v>
       </c>
       <c r="C180" s="7">
         <v>46251</v>
       </c>
       <c r="D180" s="8" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="F180" s="6">
         <v>695.25</v>
@@ -7804,19 +7014,19 @@
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="C181" s="7">
         <v>46241</v>
       </c>
       <c r="D181" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="F181" s="6">
         <v>2.2000000000000002</v>
@@ -7830,19 +7040,19 @@
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="C182" s="7">
         <v>46241</v>
       </c>
       <c r="D182" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E182" s="8" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F182" s="6">
         <v>0</v>
@@ -7856,19 +7066,19 @@
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B183" s="8" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="C183" s="7">
         <v>46244</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E183" s="8" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F183" s="6">
         <v>7.99</v>
@@ -7882,19 +7092,19 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="8" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="C184" s="7">
         <v>46244</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E184" s="8" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F184" s="6">
         <v>0</v>
@@ -7907,642 +7117,640 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H184" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C49D9B-F237-4E57-8F1A-F53EF35CD8D6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16" style="8" customWidth="1"/>
-    <col min="2" max="9" width="18.28515625" style="8" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" style="8" customWidth="1"/>
-    <col min="11" max="11" width="20.5703125" style="8" customWidth="1"/>
-    <col min="12" max="16384" width="10.28515625" style="8"/>
+    <col min="2" max="9" width="18.33203125" style="8" customWidth="1"/>
+    <col min="10" max="10" width="22.88671875" style="8" customWidth="1"/>
+    <col min="11" max="11" width="20.5546875" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="30" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:11" ht="24" customHeight="1">
+      <c r="A1" s="41" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-    </row>
-    <row r="2" spans="1:11" ht="27.95" customHeight="1">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.35" customHeight="1">
+      <c r="A2" s="42" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="B3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-    </row>
-    <row r="4" spans="1:11" ht="26.1" customHeight="1">
-      <c r="A4" s="20" t="s">
+      <c r="D3" s="39"/>
+      <c r="E3" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3" s="39"/>
+      <c r="G3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="I3" s="39"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:11" ht="20.85" customHeight="1">
+      <c r="A4" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>164</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="H4" s="21" t="s">
-        <v>232</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>273</v>
-      </c>
-      <c r="J4" s="20" t="s">
+      <c r="D4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="K4" s="20" t="s">
+      <c r="K4" s="14" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="21" customHeight="1">
-      <c r="A5" s="22">
+    <row r="5" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A5" s="16">
         <v>46235</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="17">
         <v>124.3</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17">
         <v>176.16</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="17">
         <v>1015.83</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="17">
         <v>8400</v>
       </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="24">
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="18">
         <v>9716.2900000000009</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="26">
+    <row r="6" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A6" s="20">
         <v>46236</v>
       </c>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="24">
-        <v>0</v>
-      </c>
-      <c r="K6" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="22">
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="18">
+        <v>0</v>
+      </c>
+      <c r="K6" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A7" s="16">
         <v>46237</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="17">
         <v>333.35</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23">
+      <c r="C7" s="17"/>
+      <c r="D7" s="17">
         <v>508.93</v>
       </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="23">
+      <c r="E7" s="17"/>
+      <c r="F7" s="17">
         <v>940.8</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="17">
         <v>560.48</v>
       </c>
-      <c r="H7" s="23"/>
-      <c r="I7" s="23"/>
-      <c r="J7" s="24">
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="18">
         <v>2343.56</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="26">
+    <row r="8" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A8" s="20">
         <v>46238</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="21">
         <v>1929.79</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="21">
         <v>985.6</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="21">
         <v>160</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="21">
         <v>827.16</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="21">
         <v>211.31</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="21">
         <v>57.63</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="21">
         <v>124.3</v>
       </c>
-      <c r="I8" s="27"/>
-      <c r="J8" s="24">
+      <c r="I8" s="21"/>
+      <c r="J8" s="18">
         <v>4295.79</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="22">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="22">
+    <row r="9" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A9" s="16">
         <v>46239</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="17">
         <v>197.75</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23">
+      <c r="C9" s="17"/>
+      <c r="D9" s="17">
         <v>100</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="17">
         <v>45.2</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="17">
         <v>824.9</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23">
+      <c r="G9" s="17"/>
+      <c r="H9" s="17">
         <v>335.61</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="24">
+      <c r="I9" s="17"/>
+      <c r="J9" s="18">
         <v>1503.46</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="19">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="26">
+    <row r="10" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A10" s="20">
         <v>46240</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="21">
         <v>622.82000000000005</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="24">
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="18">
         <v>622.82000000000005</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="22">
+    <row r="11" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A11" s="16">
         <v>46241</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="17">
         <v>1115.8800000000001</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="17">
         <v>67.8</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="17">
         <v>461.98</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="17">
         <v>1021.92</v>
       </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17">
         <v>76.84</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23">
+      <c r="H11" s="17"/>
+      <c r="I11" s="17">
         <v>22.02</v>
       </c>
-      <c r="J11" s="24">
+      <c r="J11" s="18">
         <v>2766.44</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="19">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="26">
+    <row r="12" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A12" s="20">
         <v>46242</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21">
         <v>814.73</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="24">
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="18">
         <v>814.73</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="22">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="21" customHeight="1">
-      <c r="A13" s="22">
+    <row r="13" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A13" s="16">
         <v>46243</v>
       </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="24">
-        <v>0</v>
-      </c>
-      <c r="K13" s="25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="21" customHeight="1">
-      <c r="A14" s="26">
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="18">
+        <v>0</v>
+      </c>
+      <c r="K13" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A14" s="20">
         <v>46244</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="21">
         <v>716.42</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="21">
         <v>113.14</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="21">
         <v>267.26</v>
       </c>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27">
+      <c r="E14" s="21"/>
+      <c r="F14" s="21">
         <v>911.91</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="21">
         <v>554.83000000000004</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="21">
         <v>192.1</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="21">
         <v>79.89</v>
       </c>
-      <c r="J14" s="24">
+      <c r="J14" s="18">
         <v>2835.55</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="22">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="21" customHeight="1">
-      <c r="A15" s="22">
+    <row r="15" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A15" s="16">
         <v>46245</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="17">
         <v>904</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="17">
         <v>372.9</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="17">
         <v>604.79999999999995</v>
       </c>
-      <c r="E15" s="23">
-        <v>0</v>
-      </c>
-      <c r="F15" s="23">
+      <c r="E15" s="17">
+        <v>0</v>
+      </c>
+      <c r="F15" s="17">
         <v>225.25</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="17">
         <v>552.16</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="17">
         <v>30319</v>
       </c>
-      <c r="I15" s="23"/>
-      <c r="J15" s="24">
+      <c r="I15" s="17"/>
+      <c r="J15" s="18">
         <v>32978.11</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="19">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="21" customHeight="1">
-      <c r="A16" s="26">
+    <row r="16" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A16" s="20">
         <v>46246</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="21">
         <v>6110.3</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27">
+      <c r="C16" s="21"/>
+      <c r="D16" s="21">
         <v>729.98</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="21">
         <v>640.59</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="21">
         <v>281.29000000000002</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="21">
         <v>56.5</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="21">
         <v>544.59</v>
       </c>
-      <c r="I16" s="27"/>
-      <c r="J16" s="24">
+      <c r="I16" s="21"/>
+      <c r="J16" s="18">
         <v>8363.25</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="22">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="21" customHeight="1">
-      <c r="A17" s="22">
+    <row r="17" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A17" s="16">
         <v>46247</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B17" s="17">
         <v>604.86</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="17">
         <v>1.38</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23">
+      <c r="D17" s="17"/>
+      <c r="E17" s="17">
         <v>169.3</v>
       </c>
-      <c r="F17" s="23">
+      <c r="F17" s="17">
         <v>564.08000000000004</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="17">
         <v>1681.24</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="17">
         <v>216.96</v>
       </c>
-      <c r="I17" s="23"/>
-      <c r="J17" s="24">
+      <c r="I17" s="17"/>
+      <c r="J17" s="18">
         <v>3237.82</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="19">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="21" customHeight="1">
-      <c r="A18" s="26">
+    <row r="18" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A18" s="20">
         <v>46248</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="21">
         <v>9077.44</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="21">
         <v>66.67</v>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="21">
         <v>25.99</v>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="21">
         <v>1893.46</v>
       </c>
-      <c r="F18" s="27">
-        <v>0</v>
-      </c>
-      <c r="G18" s="27">
+      <c r="F18" s="21">
+        <v>0</v>
+      </c>
+      <c r="G18" s="21">
         <v>335.61</v>
       </c>
-      <c r="H18" s="27">
-        <v>0</v>
-      </c>
-      <c r="I18" s="27"/>
-      <c r="J18" s="24">
+      <c r="H18" s="21">
+        <v>0</v>
+      </c>
+      <c r="I18" s="21"/>
+      <c r="J18" s="18">
         <v>11399.17</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="22">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="21" customHeight="1">
-      <c r="A19" s="22">
+    <row r="19" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A19" s="16">
         <v>46249</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23">
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17">
         <v>532.23</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="17">
         <v>40.99</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="17">
         <v>84.75</v>
       </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23">
+      <c r="G19" s="17"/>
+      <c r="H19" s="17">
         <v>244.08</v>
       </c>
-      <c r="I19" s="23"/>
-      <c r="J19" s="24">
+      <c r="I19" s="17"/>
+      <c r="J19" s="18">
         <v>902.05</v>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="21" customHeight="1">
-      <c r="A20" s="26">
+    <row r="20" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A20" s="20">
         <v>46250</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="21">
         <v>282.5</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27">
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21">
         <v>237.34</v>
       </c>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="24">
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="18">
         <v>519.84</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="22">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="21" customHeight="1">
-      <c r="A21" s="22">
+    <row r="21" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A21" s="16">
         <v>46251</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="17">
         <v>387.59</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="17">
         <v>21.47</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="17">
         <v>793.26</v>
       </c>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23">
+      <c r="E21" s="17"/>
+      <c r="F21" s="17">
         <v>637.25</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="17">
         <v>966.05</v>
       </c>
-      <c r="H21" s="23">
+      <c r="H21" s="17">
         <v>728.06</v>
       </c>
-      <c r="I21" s="23"/>
-      <c r="J21" s="24">
+      <c r="I21" s="17"/>
+      <c r="J21" s="18">
         <v>3533.68</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="19">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="21" customHeight="1">
-      <c r="A22" s="26">
+    <row r="22" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A22" s="20">
         <v>46252</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="21">
         <v>1671.29</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="21">
         <v>6163.5</v>
       </c>
-      <c r="D22" s="27">
+      <c r="D22" s="21">
         <v>339</v>
       </c>
-      <c r="E22" s="27">
+      <c r="E22" s="21">
         <v>307.38</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27">
+      <c r="F22" s="21"/>
+      <c r="G22" s="21">
         <v>310.24</v>
       </c>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="24">
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="18">
         <v>8791.41</v>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="22">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="21" customHeight="1">
-      <c r="A23" s="22">
+    <row r="23" spans="1:11" ht="16.8" customHeight="1">
+      <c r="A23" s="16">
         <v>46253</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="17">
         <v>371.77</v>
       </c>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23">
+      <c r="C23" s="17"/>
+      <c r="D23" s="17">
         <v>56.5</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="17">
         <v>2093.02</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="17">
         <v>5251.38</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="17">
         <v>485.25</v>
       </c>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="24">
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="18">
         <v>8257.92</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="19">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K23" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="5">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
@@ -8555,762 +7763,797 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60CE6AC7-E934-44A4-BAA8-C3549F7AB69B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.140625" style="8" customWidth="1"/>
-    <col min="2" max="4" width="20.5703125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="3.42578125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="22.85546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" style="8" customWidth="1"/>
+    <col min="2" max="4" width="20.5546875" style="8" customWidth="1"/>
+    <col min="5" max="5" width="3.44140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="22.88671875" style="8" customWidth="1"/>
     <col min="7" max="7" width="16" style="8" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" style="8" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="8"/>
-    <col min="10" max="17" width="13.7109375" style="8" customWidth="1"/>
-    <col min="18" max="23" width="10.28515625" style="8"/>
-    <col min="24" max="25" width="2.28515625" style="8" customWidth="1"/>
-    <col min="26" max="16384" width="10.28515625" style="8"/>
+    <col min="8" max="8" width="20.5546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" style="8"/>
+    <col min="10" max="17" width="13.6640625" style="8" customWidth="1"/>
+    <col min="18" max="23" width="10.33203125" style="8"/>
+    <col min="24" max="25" width="2.33203125" style="8" customWidth="1"/>
+    <col min="26" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="32.1" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:25" ht="25.65" customHeight="1">
+      <c r="A1" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="X1" s="29" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="X1" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="Y1" s="29" t="s">
+      <c r="Y1" s="37" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="27.95" customHeight="1">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:25" ht="22.35" customHeight="1">
+      <c r="A2" s="42" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="X2" s="29" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="X2" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="Y2" s="29">
+      <c r="Y2" s="37">
         <f t="shared" ref="Y2:Y20" si="0">B15</f>
         <v>9716.2900000000009</v>
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="X3" s="29" t="s">
+      <c r="X3" s="23" t="s">
         <v>297</v>
       </c>
-      <c r="Y3" s="29">
+      <c r="Y3" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="H4" s="20"/>
-      <c r="X4" s="29" t="s">
+      <c r="H4" s="14"/>
+      <c r="X4" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="Y4" s="29">
+      <c r="Y4" s="37">
         <f t="shared" si="0"/>
         <v>2343.56</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="15" customHeight="1">
-      <c r="A5" s="30">
+    <row r="5" spans="1:25" ht="12" customHeight="1">
+      <c r="A5" s="49">
         <v>46235</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="30">
+      <c r="B5" s="39"/>
+      <c r="C5" s="49">
         <v>46253</v>
       </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="31" t="s">
+      <c r="D5" s="39"/>
+      <c r="E5" s="50" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="32" t="s">
+      <c r="F5" s="39"/>
+      <c r="G5" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="H5" s="10"/>
-      <c r="X5" s="29" t="s">
+      <c r="H5" s="39"/>
+      <c r="X5" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="Y5" s="29">
+      <c r="Y5" s="37">
         <f t="shared" si="0"/>
         <v>4295.79</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="X6" s="29" t="s">
+      <c r="X6" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="Y6" s="29">
+      <c r="Y6" s="37">
         <f t="shared" si="0"/>
         <v>1503.46</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
-      <c r="A7" s="18" t="s">
+    <row r="7" spans="1:25" ht="14.4">
+      <c r="A7" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="13"/>
+      <c r="E7" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18" t="s">
+      <c r="F7" s="13"/>
+      <c r="G7" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="X7" s="29" t="s">
+      <c r="H7" s="13"/>
+      <c r="I7" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="J7" s="53"/>
+      <c r="X7" s="23" t="s">
         <v>309</v>
       </c>
-      <c r="Y7" s="29">
+      <c r="Y7" s="37">
         <f t="shared" si="0"/>
         <v>622.82000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="19.5" customHeight="1">
-      <c r="A8" s="33">
+    <row r="8" spans="1:25" ht="15.6" customHeight="1">
+      <c r="A8" s="44">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="33">
+      <c r="B8" s="45"/>
+      <c r="C8" s="44">
         <f>IFERROR(AVERAGEIF(H15:H22,"&gt;0"),0)</f>
         <v>12860.23625</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="33">
+      <c r="D8" s="45"/>
+      <c r="E8" s="44">
         <f>IFERROR(MAX(H15:H22),0)</f>
         <v>32704.7</v>
       </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="34">
+      <c r="F8" s="45"/>
+      <c r="G8" s="46">
         <f>COUNTIF(H15:H22,"&gt;0")</f>
         <v>8</v>
       </c>
-      <c r="H8" s="10"/>
-      <c r="X8" s="29" t="s">
+      <c r="H8" s="47"/>
+      <c r="I8" s="54">
+        <f>IF($E$5&lt;&gt;"TODAS",SUMIF('SALDOS POR CUENTA'!$B$5:$B$100,$E$5,'SALDOS POR CUENTA'!$D$5:$D$100),IF($G$5&lt;&gt;"TODOS",SUMIF('SALDOS POR CUENTA'!$A$5:$A$100,"*"&amp;SUBSTITUTE(TRIM($G$5),"BANCO ","")&amp;"*",'SALDOS POR CUENTA'!$D$5:$D$100),SUM('SALDOS POR CUENTA'!$D$5:$D$100)))</f>
+        <v>268945.52</v>
+      </c>
+      <c r="J8" s="54"/>
+      <c r="X8" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="Y8" s="29">
+      <c r="Y8" s="37">
         <f t="shared" si="0"/>
         <v>2766.44</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="X9" s="29" t="s">
+      <c r="X9" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="Y9" s="29">
+      <c r="Y9" s="37">
         <f t="shared" si="0"/>
         <v>814.73</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="8.1" customHeight="1">
-      <c r="A10" s="35"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="X10" s="29" t="s">
+    <row r="10" spans="1:25" ht="6.45" customHeight="1">
+      <c r="A10" s="24"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="X10" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="Y10" s="29">
+      <c r="Y10" s="37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="X11" s="29" t="s">
+      <c r="X11" s="23" t="s">
         <v>313</v>
       </c>
-      <c r="Y11" s="29">
+      <c r="Y11" s="37">
         <f t="shared" si="0"/>
         <v>2835.55</v>
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="X12" s="29" t="s">
+      <c r="X12" s="23" t="s">
         <v>314</v>
       </c>
-      <c r="Y12" s="29">
+      <c r="Y12" s="37">
         <f t="shared" si="0"/>
         <v>32978.11</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15" customHeight="1">
-      <c r="A13" s="36" t="s">
+    <row r="13" spans="1:25" ht="12" customHeight="1">
+      <c r="A13" s="48" t="s">
         <v>315</v>
       </c>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="F13" s="36" t="s">
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="F13" s="48" t="s">
         <v>316</v>
       </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="X13" s="29" t="s">
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="X13" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="Y13" s="29">
+      <c r="Y13" s="37">
         <f t="shared" si="0"/>
         <v>8363.25</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="20" t="s">
+      <c r="F14" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="X14" s="29" t="s">
+      <c r="X14" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="Y14" s="29">
+      <c r="Y14" s="37">
         <f t="shared" si="0"/>
         <v>3237.82</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A5&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A5&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A5,"")</f>
+      <c r="A15" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A5&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A5&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A5,"")</f>
         <v>46235</v>
       </c>
-      <c r="B15" s="38">
-        <f>IF(A15="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A15,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A15,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B15" s="35">
+        <f>IF(A15="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A15,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A15,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>9716.2900000000009</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="35">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D15" s="39">
-        <f>IF(A15="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A15,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B15&gt;0,1,0)))</f>
+      <c r="D15" s="26">
+        <f>IF(A15="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A15,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B15&gt;0,1,0)))</f>
         <v>4</v>
       </c>
-      <c r="F15" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="38">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F15)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G15,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$B$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="F15" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="H15" s="35">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F15)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G15,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$B$5:$B$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>24450.060000000005</v>
       </c>
-      <c r="X15" s="29" t="s">
+      <c r="X15" s="23" t="s">
         <v>323</v>
       </c>
-      <c r="Y15" s="29">
+      <c r="Y15" s="37">
         <f t="shared" si="0"/>
         <v>11399.17</v>
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A6&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A6&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A6,"")</f>
+      <c r="A16" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A6&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A6&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A6,"")</f>
         <v>46236</v>
       </c>
-      <c r="B16" s="43">
-        <f>IF(A16="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A16,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A16,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="43">
+      <c r="B16" s="36">
+        <f>IF(A16="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A16,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A16,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="36">
         <f t="shared" ref="C16:C33" si="1">B16-B15</f>
         <v>-9716.2900000000009</v>
       </c>
-      <c r="D16" s="44">
-        <f>IF(A16="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A16,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B16&gt;0,1,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="45" t="s">
+      <c r="D16" s="30">
+        <f>IF(A16="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A16,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B16&gt;0,1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="G16" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="43">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F16)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G16,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$C$5:$C$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="G16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="36">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F16)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G16,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$C$5:$C$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>7792.46</v>
       </c>
-      <c r="X16" s="29" t="s">
+      <c r="X16" s="23" t="s">
         <v>324</v>
       </c>
-      <c r="Y16" s="29">
+      <c r="Y16" s="37">
         <f t="shared" si="0"/>
         <v>902.05</v>
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A7&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A7&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A7,"")</f>
+      <c r="A17" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A7&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A7&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A7,"")</f>
         <v>46237</v>
       </c>
-      <c r="B17" s="38">
-        <f>IF(A17="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A17,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A17,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B17" s="35">
+        <f>IF(A17="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A17,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A17,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>2343.56</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="35">
         <f t="shared" si="1"/>
         <v>2343.56</v>
       </c>
-      <c r="D17" s="39">
-        <f>IF(A17="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A17,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B17&gt;0,1,0)))</f>
+      <c r="D17" s="26">
+        <f>IF(A17="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A17,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B17&gt;0,1,0)))</f>
         <v>4</v>
       </c>
-      <c r="F17" s="40" t="s">
+      <c r="F17" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="G17" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="38">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F17)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G17,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$D$5:$D$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="G17" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" s="35">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F17)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G17,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$D$5:$D$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>4756.09</v>
       </c>
-      <c r="X17" s="29" t="s">
+      <c r="X17" s="23" t="s">
         <v>325</v>
       </c>
-      <c r="Y17" s="29">
+      <c r="Y17" s="37">
         <f t="shared" si="0"/>
         <v>519.84</v>
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A8&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A8&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A8,"")</f>
+      <c r="A18" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A8&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A8&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A8,"")</f>
         <v>46238</v>
       </c>
-      <c r="B18" s="43">
-        <f>IF(A18="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A18,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A18,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B18" s="36">
+        <f>IF(A18="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A18,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A18,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>4295.79</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="36">
         <f t="shared" si="1"/>
         <v>1952.23</v>
       </c>
-      <c r="D18" s="44">
-        <f>IF(A18="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A18,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B18&gt;0,1,0)))</f>
+      <c r="D18" s="30">
+        <f>IF(A18="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A18,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B18&gt;0,1,0)))</f>
         <v>7</v>
       </c>
-      <c r="F18" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="G18" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="43">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F18)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G18,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$E$5:$E$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="F18" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="36">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F18)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G18,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$E$5:$E$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>9106.92</v>
       </c>
-      <c r="X18" s="29" t="s">
+      <c r="X18" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="Y18" s="29">
+      <c r="Y18" s="37">
         <f t="shared" si="0"/>
         <v>3533.68</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A9&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A9&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A9,"")</f>
+      <c r="A19" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A9&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A9&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A9,"")</f>
         <v>46239</v>
       </c>
-      <c r="B19" s="38">
-        <f>IF(A19="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A19,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A19,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B19" s="35">
+        <f>IF(A19="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A19,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A19,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>1503.46</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="35">
         <f t="shared" si="1"/>
         <v>-2792.33</v>
       </c>
-      <c r="D19" s="39">
-        <f>IF(A19="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A19,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B19&gt;0,1,0)))</f>
+      <c r="D19" s="26">
+        <f>IF(A19="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A19,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B19&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-      <c r="F19" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="H19" s="38">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F19)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G19,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$F$5:$F$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="F19" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="G19" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="35">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F19)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G19,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$F$5:$F$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>18332.919999999998</v>
       </c>
-      <c r="X19" s="29" t="s">
+      <c r="X19" s="23" t="s">
         <v>327</v>
       </c>
-      <c r="Y19" s="29">
+      <c r="Y19" s="37">
         <f t="shared" si="0"/>
         <v>8791.41</v>
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A10&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A10&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A10,"")</f>
+      <c r="A20" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A10&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A10&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A10,"")</f>
         <v>46240</v>
       </c>
-      <c r="B20" s="43">
-        <f>IF(A20="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A20,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A20,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B20" s="36">
+        <f>IF(A20="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A20,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A20,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>622.82000000000005</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="36">
         <f t="shared" si="1"/>
         <v>-880.64</v>
       </c>
-      <c r="D20" s="44">
-        <f>IF(A20="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A20,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B20&gt;0,1,0)))</f>
+      <c r="D20" s="30">
+        <f>IF(A20="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A20,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B20&gt;0,1,0)))</f>
         <v>1</v>
       </c>
-      <c r="F20" s="45" t="s">
-        <v>219</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="H20" s="43">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F20)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G20,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$G$5:$G$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="F20" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="36">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F20)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G20,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$G$5:$G$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>5636.83</v>
       </c>
-      <c r="X20" s="29" t="s">
+      <c r="X20" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="Y20" s="29">
+      <c r="Y20" s="37">
         <f t="shared" si="0"/>
         <v>8257.92</v>
       </c>
     </row>
-    <row r="21" spans="1:25">
-      <c r="A21" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A11&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A11&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A11,"")</f>
+    <row r="21" spans="1:25" ht="14.4">
+      <c r="A21" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A11&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A11&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A11,"")</f>
         <v>46241</v>
       </c>
-      <c r="B21" s="38">
-        <f>IF(A21="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A21,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A21,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B21" s="35">
+        <f>IF(A21="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A21,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A21,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>2766.44</v>
       </c>
-      <c r="C21" s="38">
+      <c r="C21" s="35">
         <f t="shared" si="1"/>
         <v>2143.62</v>
       </c>
-      <c r="D21" s="39">
-        <f>IF(A21="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A21,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B21&gt;0,1,0)))</f>
+      <c r="D21" s="26">
+        <f>IF(A21="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A21,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B21&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-      <c r="F21" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="G21" s="41" t="s">
-        <v>232</v>
-      </c>
-      <c r="H21" s="38">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F21)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G21,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$H$5:$H$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="F21" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="35">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F21)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G21,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$H$5:$H$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>32704.7</v>
       </c>
-    </row>
-    <row r="22" spans="1:25">
-      <c r="A22" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A12&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A12&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A12,"")</f>
+      <c r="Y21" s="33"/>
+    </row>
+    <row r="22" spans="1:25" ht="14.4">
+      <c r="A22" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A12&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A12&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A12,"")</f>
         <v>46242</v>
       </c>
-      <c r="B22" s="43">
-        <f>IF(A22="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A22,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A22,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B22" s="36">
+        <f>IF(A22="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A22,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A22,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>814.73</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="36">
         <f t="shared" si="1"/>
         <v>-1951.71</v>
       </c>
-      <c r="D22" s="44">
-        <f>IF(A22="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A22,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B22&gt;0,1,0)))</f>
+      <c r="D22" s="30">
+        <f>IF(A22="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A22,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B22&gt;0,1,0)))</f>
         <v>1</v>
       </c>
-      <c r="F22" s="45" t="s">
-        <v>231</v>
-      </c>
-      <c r="G22" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="H22" s="43">
-        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F22)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G22,"0"))),SUMIFS('[1]REPORTE CREDITOS DIARIOS (2)'!$I$5:$I$23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&gt;="&amp;$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
+      <c r="F22" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="36">
+        <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F22)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G22,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$I$5:$I$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>101.91</v>
       </c>
-    </row>
-    <row r="23" spans="1:25">
-      <c r="A23" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A13&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A13&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A13,"")</f>
+      <c r="Y22" s="33"/>
+    </row>
+    <row r="23" spans="1:25" ht="14.4">
+      <c r="A23" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A13&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A13&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A13,"")</f>
         <v>46243</v>
       </c>
-      <c r="B23" s="38">
-        <f>IF(A23="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A23,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
-        <v>0</v>
-      </c>
-      <c r="C23" s="38">
+      <c r="B23" s="35">
+        <f>IF(A23="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A23,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
+        <v>0</v>
+      </c>
+      <c r="C23" s="35">
         <f t="shared" si="1"/>
         <v>-814.73</v>
       </c>
-      <c r="D23" s="39">
-        <f>IF(A23="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A23,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B23&gt;0,1,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="47" t="s">
-        <v>329</v>
-      </c>
-      <c r="G23" s="47"/>
-      <c r="H23" s="48">
+      <c r="D23" s="26">
+        <f>IF(A23="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B23&gt;0,1,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>331</v>
+      </c>
+      <c r="G23" s="52"/>
+      <c r="H23" s="34">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
       </c>
-    </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A14&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A14&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A14,"")</f>
+      <c r="Y23" s="33"/>
+    </row>
+    <row r="24" spans="1:25" ht="14.4">
+      <c r="A24" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A14&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A14&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A14,"")</f>
         <v>46244</v>
       </c>
-      <c r="B24" s="43">
-        <f>IF(A24="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A24,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A24,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B24" s="36">
+        <f>IF(A24="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A24,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A24,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>2835.55</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="36">
         <f t="shared" si="1"/>
         <v>2835.55</v>
       </c>
-      <c r="D24" s="44">
-        <f>IF(A24="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A24,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B24&gt;0,1,0)))</f>
+      <c r="D24" s="30">
+        <f>IF(A24="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A24,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B24&gt;0,1,0)))</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="25" spans="1:25">
-      <c r="A25" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A15&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A15&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A15,"")</f>
+      <c r="Y24" s="33"/>
+    </row>
+    <row r="25" spans="1:25" ht="14.4">
+      <c r="A25" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A15&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A15&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A15,"")</f>
         <v>46245</v>
       </c>
-      <c r="B25" s="38">
-        <f>IF(A25="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A25,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A25,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B25" s="35">
+        <f>IF(A25="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A25,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A25,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>32978.11</v>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="35">
         <f t="shared" si="1"/>
         <v>30142.560000000001</v>
       </c>
-      <c r="D25" s="39">
-        <f>IF(A25="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A25,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B25&gt;0,1,0)))</f>
+      <c r="D25" s="26">
+        <f>IF(A25="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A25,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B25&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A16&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A16&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A16,"")</f>
+      <c r="Y25" s="33"/>
+    </row>
+    <row r="26" spans="1:25" ht="14.4">
+      <c r="A26" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A16&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A16&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A16,"")</f>
         <v>46246</v>
       </c>
-      <c r="B26" s="43">
-        <f>IF(A26="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A26,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A26,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B26" s="36">
+        <f>IF(A26="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A26,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A26,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>8363.25</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="36">
         <f t="shared" si="1"/>
         <v>-24614.86</v>
       </c>
-      <c r="D26" s="44">
-        <f>IF(A26="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A26,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B26&gt;0,1,0)))</f>
+      <c r="D26" s="30">
+        <f>IF(A26="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A26,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B26&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:25">
-      <c r="A27" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A17&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A17&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A17,"")</f>
+      <c r="Y26" s="33"/>
+    </row>
+    <row r="27" spans="1:25" ht="14.4">
+      <c r="A27" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A17&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A17&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A17,"")</f>
         <v>46247</v>
       </c>
-      <c r="B27" s="38">
-        <f>IF(A27="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A27,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A27,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B27" s="35">
+        <f>IF(A27="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A27,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A27,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>3237.82</v>
       </c>
-      <c r="C27" s="38">
+      <c r="C27" s="35">
         <f t="shared" si="1"/>
         <v>-5125.43</v>
       </c>
-      <c r="D27" s="39">
-        <f>IF(A27="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A27,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B27&gt;0,1,0)))</f>
+      <c r="D27" s="26">
+        <f>IF(A27="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A27,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B27&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:25">
-      <c r="A28" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A18&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A18&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A18,"")</f>
+      <c r="Y27" s="33"/>
+    </row>
+    <row r="28" spans="1:25" ht="14.4">
+      <c r="A28" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A18&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A18&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A18,"")</f>
         <v>46248</v>
       </c>
-      <c r="B28" s="43">
-        <f>IF(A28="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A28,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A28,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B28" s="36">
+        <f>IF(A28="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A28,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A28,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>11399.17</v>
       </c>
-      <c r="C28" s="43">
+      <c r="C28" s="36">
         <f t="shared" si="1"/>
         <v>8161.35</v>
       </c>
-      <c r="D28" s="44">
-        <f>IF(A28="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A28,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B28&gt;0,1,0)))</f>
+      <c r="D28" s="30">
+        <f>IF(A28="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A28,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B28&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="29" spans="1:25">
-      <c r="A29" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A19&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A19&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A19,"")</f>
+      <c r="Y28" s="33"/>
+    </row>
+    <row r="29" spans="1:25" ht="14.4">
+      <c r="A29" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A19&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A19&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A19,"")</f>
         <v>46249</v>
       </c>
-      <c r="B29" s="38">
-        <f>IF(A29="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A29,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A29,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B29" s="35">
+        <f>IF(A29="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A29,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A29,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>902.05</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="35">
         <f t="shared" si="1"/>
         <v>-10497.12</v>
       </c>
-      <c r="D29" s="39">
-        <f>IF(A29="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A29,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B29&gt;0,1,0)))</f>
+      <c r="D29" s="26">
+        <f>IF(A29="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A29,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B29&gt;0,1,0)))</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="1:25">
-      <c r="A30" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A20&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A20&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A20,"")</f>
+      <c r="Y29" s="33"/>
+    </row>
+    <row r="30" spans="1:25" ht="14.4">
+      <c r="A30" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A20&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A20&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A20,"")</f>
         <v>46250</v>
       </c>
-      <c r="B30" s="43">
-        <f>IF(A30="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A30,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A30,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B30" s="36">
+        <f>IF(A30="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A30,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A30,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>519.84</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="36">
         <f t="shared" si="1"/>
         <v>-382.20999999999992</v>
       </c>
-      <c r="D30" s="44">
-        <f>IF(A30="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A30,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B30&gt;0,1,0)))</f>
+      <c r="D30" s="30">
+        <f>IF(A30="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A30,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B30&gt;0,1,0)))</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:25">
-      <c r="A31" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A21&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A21&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A21,"")</f>
+      <c r="Y30" s="33"/>
+    </row>
+    <row r="31" spans="1:25" ht="14.4">
+      <c r="A31" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A21&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A21&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A21,"")</f>
         <v>46251</v>
       </c>
-      <c r="B31" s="38">
-        <f>IF(A31="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A31,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A31,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B31" s="35">
+        <f>IF(A31="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A31,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A31,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>3533.68</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="35">
         <f t="shared" si="1"/>
         <v>3013.8399999999997</v>
       </c>
-      <c r="D31" s="39">
-        <f>IF(A31="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A31,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B31&gt;0,1,0)))</f>
+      <c r="D31" s="26">
+        <f>IF(A31="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A31,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B31&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="32" spans="1:25">
-      <c r="A32" s="42">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A22&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A22&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A22,"")</f>
+      <c r="Y31" s="33"/>
+    </row>
+    <row r="32" spans="1:25" ht="14.4">
+      <c r="A32" s="29">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A22&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A22&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A22,"")</f>
         <v>46252</v>
       </c>
-      <c r="B32" s="43">
-        <f>IF(A32="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A32,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A32,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B32" s="36">
+        <f>IF(A32="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A32,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A32,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>8791.41</v>
       </c>
-      <c r="C32" s="43">
+      <c r="C32" s="36">
         <f t="shared" si="1"/>
         <v>5257.73</v>
       </c>
-      <c r="D32" s="44">
-        <f>IF(A32="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A32,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B32&gt;0,1,0)))</f>
+      <c r="D32" s="30">
+        <f>IF(A32="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A32,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B32&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="37">
-        <f>IF(AND('[1]REPORTE CREDITOS DIARIOS (2)'!A23&gt;=$A$5,'[1]REPORTE CREDITOS DIARIOS (2)'!A23&lt;=$C$5),'[1]REPORTE CREDITOS DIARIOS (2)'!A23,"")</f>
+      <c r="Y32" s="33"/>
+    </row>
+    <row r="33" spans="1:25" ht="14.4">
+      <c r="A33" s="25">
+        <f>IF(AND('REPORTE CREDITOS DIARIOS'!A23&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A23&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A23,"")</f>
         <v>46253</v>
       </c>
-      <c r="B33" s="38">
-        <f>IF(A33="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$B$5:$I$23,MATCH(A33,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0),MATCH($E$5,'[1]REPORTE CREDITOS DIARIOS (2)'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,A33,'[1]REPORTE CREDITOS DIARIOS (2)'!$J$5:$J$23),0),0)))</f>
+      <c r="B33" s="35">
+        <f>IF(A33="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A33,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A33,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>8257.92</v>
       </c>
-      <c r="C33" s="38">
+      <c r="C33" s="35">
         <f t="shared" si="1"/>
         <v>-533.48999999999978</v>
       </c>
-      <c r="D33" s="39">
-        <f>IF(A33="",0,IF($G$5="TODOS",IFERROR(INDEX('[1]REPORTE CREDITOS DIARIOS (2)'!$K$5:$K$23,MATCH(A33,'[1]REPORTE CREDITOS DIARIOS (2)'!$A$5:$A$23,0)),0),IF(B33&gt;0,1,0)))</f>
+      <c r="D33" s="26">
+        <f>IF(A33="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A33,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B33&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="Y33" s="33"/>
+    </row>
+    <row r="34" spans="1:25" ht="14.4">
+      <c r="Y34" s="33"/>
+    </row>
+    <row r="35" spans="1:25" ht="14.4">
+      <c r="A35" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="Y35" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
@@ -9318,12 +8561,6 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="F13:H13"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="H15:H22">
     <cfRule type="dataBar" priority="1">
@@ -9342,17 +8579,17 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="E5" xr:uid="{6C4E363A-C1FD-466B-9756-B0FF7A088509}">
+    <dataValidation type="list" sqref="E5" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TODAS,9596,2509,4978,0386,6715,0049,8202,1962"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G5" xr:uid="{0D487BCF-1041-4F82-8ED1-B0F6B168DCBA}">
+    <dataValidation type="list" sqref="G5" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"TODOS,BANCO AGRÍCOLA,BANCO CUSCATLÁN,BAC,PROMERICA,DAVIVIENDA"</formula1>
     </dataValidation>
-    <dataValidation type="date" sqref="A5 C5" xr:uid="{635AC23D-41ED-4D22-9201-3F953BC3B084}">
+    <dataValidation type="date" sqref="A5 C5" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>DATE(2026,1,1)</formula1>
       <formula2>DATE(2030,12,31)</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="G5" xr:uid="{AF784880-B382-42CD-9570-F3051FF335F0}">
+    <dataValidation type="list" sqref="G5" xr:uid="{00000000-0002-0000-0300-000003000000}">
       <formula1>"TODOS,AGRÍCOLA,CUSCATLÁN,BAC,PROMERICA,DAVIVIENDA"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
+++ b/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Gonzalez\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C6B073-D9B6-4D15-8F5E-B776CFF27F96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40780563-218B-40B3-9B54-BB45C6796549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="334">
   <si>
     <t>SALDOS INICIALES Y FINALES POR CUENTA</t>
   </si>
@@ -1025,28 +1025,35 @@
     <t>19/08</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>Nota: el reporte suma únicamente los valores existentes en Crédito / Abono / Valor +. Los movimientos originales permanecen sin cambios.</t>
   </si>
   <si>
-    <t>SALDO DISPONIBLE</t>
-  </si>
-  <si>
-    <t>Total</t>
+    <t>Dinero disponible</t>
+  </si>
+  <si>
+    <t>SALDO FINAL TOTAL</t>
+  </si>
+  <si>
+    <t>DINERO DISPONIBLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0000"/>
     <numFmt numFmtId="168" formatCode="\$#,##0.00;[Red]\-\$#,##0.00"/>
     <numFmt numFmtId="169" formatCode="\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-"/>
+    <numFmt numFmtId="170" formatCode="\Q\ #,##0.00;[Red]\-\Q\ #,##0.00"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1143,17 +1150,36 @@
       <sz val="11"/>
       <color rgb="FF008080"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="2" tint="-0.749961851863155"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF008080"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="2" tint="-0.749992370372631"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,12 +1243,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1241,13 +1273,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1269,18 +1316,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1328,6 +1363,7 @@
     <xf numFmtId="169" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1344,6 +1380,24 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1355,23 +1409,29 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1379,8 +1439,116 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </bottom>
+        <vertical style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </horizontal>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF008080"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1584,7 +1752,7 @@
           <c:smooth val="1"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6594-47E3-8145-010E8EFD41FC}"/>
+              <c16:uniqueId val="{00000000-BDED-475D-8FDA-8AF14A29C274}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1812,7 +1980,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-92AC-41A0-8F27-E22BB8285E16}"/>
+              <c16:uniqueId val="{00000000-93C6-4152-9E78-A22C24564008}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1946,12 +2114,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SaldosPorCuenta" displayName="SaldosPorCuenta" ref="A4:D12" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SaldosPorCuenta" displayName="SaldosPorCuenta" ref="A4:D12" totalsRowShown="0" headerRowDxfId="0">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Banco"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cuenta"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Saldo inicial "/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Saldo final "/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Banco" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cuenta" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Saldo inicial " dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Saldo final " dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2152,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="8" customWidth="1"/>
@@ -2161,152 +2329,745 @@
     <col min="5" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.85" customHeight="1">
-      <c r="A1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-    </row>
-    <row r="2" spans="1:4" ht="22.35" customHeight="1">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:6" ht="16.649999999999999" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+    </row>
+    <row r="2" spans="1:6" ht="17.850000000000001" customHeight="1">
+      <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-    </row>
-    <row r="4" spans="1:4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+    </row>
+    <row r="4" spans="1:6" ht="19.2" customHeight="1">
+      <c r="A4" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="54" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="E4" s="55" t="s">
+        <v>331</v>
+      </c>
+      <c r="F4" s="55"/>
+    </row>
+    <row r="5" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A5" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="58">
         <v>76663.7</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="58">
         <v>71075.34</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A6" s="10" t="s">
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+    </row>
+    <row r="6" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A6" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="58">
         <v>14148.75</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="58">
         <v>21941.21</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A7" s="10" t="s">
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+    </row>
+    <row r="7" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A7" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="58">
         <v>33171.599999999999</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="58">
         <v>28319.18</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A8" s="10" t="s">
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+    </row>
+    <row r="8" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A8" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="58">
         <v>9086.82</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="58">
         <v>6003.86</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A9" s="10" t="s">
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+    </row>
+    <row r="9" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A9" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="58">
         <v>80183.38</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="58">
         <v>81910.289999999994</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A10" s="10" t="s">
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+    </row>
+    <row r="10" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A10" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="58">
         <v>51799.49</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="58">
         <v>33700.51</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A11" s="10" t="s">
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+    </row>
+    <row r="11" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A11" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="58">
         <v>38443.89</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="58">
         <v>25869.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="16.05" customHeight="1">
-      <c r="A12" s="10" t="s">
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+    </row>
+    <row r="12" spans="1:6" ht="12.75" customHeight="1">
+      <c r="A12" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="58">
         <v>31.71</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="58">
         <v>125.63</v>
       </c>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+    </row>
+    <row r="13" spans="1:6" ht="14.4">
+      <c r="E13" s="34"/>
+    </row>
+    <row r="14" spans="1:6" ht="14.4">
+      <c r="E14" s="34"/>
+    </row>
+    <row r="15" spans="1:6" ht="14.4">
+      <c r="E15" s="34"/>
+    </row>
+    <row r="16" spans="1:6" ht="14.4">
+      <c r="E16" s="34"/>
+    </row>
+    <row r="17" spans="5:5" ht="14.4">
+      <c r="E17" s="34"/>
+    </row>
+    <row r="18" spans="5:5" ht="14.4">
+      <c r="E18" s="34"/>
+    </row>
+    <row r="19" spans="5:5" ht="14.4">
+      <c r="E19" s="34"/>
+    </row>
+    <row r="20" spans="5:5" ht="14.4">
+      <c r="E20" s="34"/>
+    </row>
+    <row r="21" spans="5:5" ht="14.4">
+      <c r="E21" s="34"/>
+    </row>
+    <row r="22" spans="5:5" ht="14.4">
+      <c r="E22" s="34"/>
+    </row>
+    <row r="23" spans="5:5" ht="14.4">
+      <c r="E23" s="34"/>
+    </row>
+    <row r="24" spans="5:5" ht="14.4">
+      <c r="E24" s="34"/>
+    </row>
+    <row r="25" spans="5:5" ht="14.4">
+      <c r="E25" s="34"/>
+    </row>
+    <row r="26" spans="5:5" ht="14.4">
+      <c r="E26" s="34"/>
+    </row>
+    <row r="27" spans="5:5" ht="14.4">
+      <c r="E27" s="34"/>
+    </row>
+    <row r="28" spans="5:5" ht="14.4">
+      <c r="E28" s="34"/>
+    </row>
+    <row r="29" spans="5:5" ht="14.4">
+      <c r="E29" s="34"/>
+    </row>
+    <row r="30" spans="5:5" ht="14.4">
+      <c r="E30" s="34"/>
+    </row>
+    <row r="31" spans="5:5" ht="14.4">
+      <c r="E31" s="34"/>
+    </row>
+    <row r="32" spans="5:5" ht="14.4">
+      <c r="E32" s="34"/>
+    </row>
+    <row r="33" spans="5:5" ht="14.4">
+      <c r="E33" s="34"/>
+    </row>
+    <row r="34" spans="5:5" ht="14.4">
+      <c r="E34" s="34"/>
+    </row>
+    <row r="35" spans="5:5" ht="14.4">
+      <c r="E35" s="34"/>
+    </row>
+    <row r="36" spans="5:5" ht="14.4">
+      <c r="E36" s="34"/>
+    </row>
+    <row r="37" spans="5:5" ht="14.4">
+      <c r="E37" s="34"/>
+    </row>
+    <row r="38" spans="5:5" ht="14.4">
+      <c r="E38" s="34"/>
+    </row>
+    <row r="39" spans="5:5" ht="14.4">
+      <c r="E39" s="34"/>
+    </row>
+    <row r="40" spans="5:5" ht="14.4">
+      <c r="E40" s="34"/>
+    </row>
+    <row r="41" spans="5:5" ht="14.4">
+      <c r="E41" s="34"/>
+    </row>
+    <row r="42" spans="5:5" ht="14.4">
+      <c r="E42" s="34"/>
+    </row>
+    <row r="43" spans="5:5" ht="14.4">
+      <c r="E43" s="34"/>
+    </row>
+    <row r="44" spans="5:5" ht="14.4">
+      <c r="E44" s="34"/>
+    </row>
+    <row r="45" spans="5:5" ht="14.4">
+      <c r="E45" s="34"/>
+    </row>
+    <row r="46" spans="5:5" ht="14.4">
+      <c r="E46" s="34"/>
+    </row>
+    <row r="47" spans="5:5" ht="14.4">
+      <c r="E47" s="34"/>
+    </row>
+    <row r="48" spans="5:5" ht="14.4">
+      <c r="E48" s="34"/>
+    </row>
+    <row r="49" spans="5:5" ht="14.4">
+      <c r="E49" s="34"/>
+    </row>
+    <row r="50" spans="5:5" ht="14.4">
+      <c r="E50" s="34"/>
+    </row>
+    <row r="51" spans="5:5" ht="14.4">
+      <c r="E51" s="34"/>
+    </row>
+    <row r="52" spans="5:5" ht="14.4">
+      <c r="E52" s="34"/>
+    </row>
+    <row r="53" spans="5:5" ht="14.4">
+      <c r="E53" s="34"/>
+    </row>
+    <row r="54" spans="5:5" ht="14.4">
+      <c r="E54" s="34"/>
+    </row>
+    <row r="55" spans="5:5" ht="14.4">
+      <c r="E55" s="34"/>
+    </row>
+    <row r="56" spans="5:5" ht="14.4">
+      <c r="E56" s="34"/>
+    </row>
+    <row r="57" spans="5:5" ht="14.4">
+      <c r="E57" s="34"/>
+    </row>
+    <row r="58" spans="5:5" ht="14.4">
+      <c r="E58" s="34"/>
+    </row>
+    <row r="59" spans="5:5" ht="14.4">
+      <c r="E59" s="34"/>
+    </row>
+    <row r="60" spans="5:5" ht="14.4">
+      <c r="E60" s="34"/>
+    </row>
+    <row r="61" spans="5:5" ht="14.4">
+      <c r="E61" s="34"/>
+    </row>
+    <row r="62" spans="5:5" ht="14.4">
+      <c r="E62" s="34"/>
+    </row>
+    <row r="63" spans="5:5" ht="14.4">
+      <c r="E63" s="34"/>
+    </row>
+    <row r="64" spans="5:5" ht="14.4">
+      <c r="E64" s="34"/>
+    </row>
+    <row r="65" spans="5:5" ht="14.4">
+      <c r="E65" s="34"/>
+    </row>
+    <row r="66" spans="5:5" ht="14.4">
+      <c r="E66" s="34"/>
+    </row>
+    <row r="67" spans="5:5" ht="14.4">
+      <c r="E67" s="34"/>
+    </row>
+    <row r="68" spans="5:5" ht="14.4">
+      <c r="E68" s="34"/>
+    </row>
+    <row r="69" spans="5:5" ht="14.4">
+      <c r="E69" s="34"/>
+    </row>
+    <row r="70" spans="5:5" ht="14.4">
+      <c r="E70" s="34"/>
+    </row>
+    <row r="71" spans="5:5" ht="14.4">
+      <c r="E71" s="34"/>
+    </row>
+    <row r="72" spans="5:5" ht="14.4">
+      <c r="E72" s="34"/>
+    </row>
+    <row r="73" spans="5:5" ht="14.4">
+      <c r="E73" s="34"/>
+    </row>
+    <row r="74" spans="5:5" ht="14.4">
+      <c r="E74" s="34"/>
+    </row>
+    <row r="75" spans="5:5" ht="14.4">
+      <c r="E75" s="34"/>
+    </row>
+    <row r="76" spans="5:5" ht="14.4">
+      <c r="E76" s="34"/>
+    </row>
+    <row r="77" spans="5:5" ht="14.4">
+      <c r="E77" s="34"/>
+    </row>
+    <row r="78" spans="5:5" ht="14.4">
+      <c r="E78" s="34"/>
+    </row>
+    <row r="79" spans="5:5" ht="14.4">
+      <c r="E79" s="34"/>
+    </row>
+    <row r="80" spans="5:5" ht="14.4">
+      <c r="E80" s="34"/>
+    </row>
+    <row r="81" spans="5:5" ht="14.4">
+      <c r="E81" s="34"/>
+    </row>
+    <row r="82" spans="5:5" ht="14.4">
+      <c r="E82" s="34"/>
+    </row>
+    <row r="83" spans="5:5" ht="14.4">
+      <c r="E83" s="34"/>
+    </row>
+    <row r="84" spans="5:5" ht="14.4">
+      <c r="E84" s="34"/>
+    </row>
+    <row r="85" spans="5:5" ht="14.4">
+      <c r="E85" s="34"/>
+    </row>
+    <row r="86" spans="5:5" ht="14.4">
+      <c r="E86" s="34"/>
+    </row>
+    <row r="87" spans="5:5" ht="14.4">
+      <c r="E87" s="34"/>
+    </row>
+    <row r="88" spans="5:5" ht="14.4">
+      <c r="E88" s="34"/>
+    </row>
+    <row r="89" spans="5:5" ht="14.4">
+      <c r="E89" s="34"/>
+    </row>
+    <row r="90" spans="5:5" ht="14.4">
+      <c r="E90" s="34"/>
+    </row>
+    <row r="91" spans="5:5" ht="14.4">
+      <c r="E91" s="34"/>
+    </row>
+    <row r="92" spans="5:5" ht="14.4">
+      <c r="E92" s="34"/>
+    </row>
+    <row r="93" spans="5:5" ht="14.4">
+      <c r="E93" s="34"/>
+    </row>
+    <row r="94" spans="5:5" ht="14.4">
+      <c r="E94" s="34"/>
+    </row>
+    <row r="95" spans="5:5" ht="14.4">
+      <c r="E95" s="34"/>
+    </row>
+    <row r="96" spans="5:5" ht="14.4">
+      <c r="E96" s="34"/>
+    </row>
+    <row r="97" spans="5:5" ht="14.4">
+      <c r="E97" s="34"/>
+    </row>
+    <row r="98" spans="5:5" ht="14.4">
+      <c r="E98" s="34"/>
+    </row>
+    <row r="99" spans="5:5" ht="14.4">
+      <c r="E99" s="34"/>
+    </row>
+    <row r="100" spans="5:5" ht="14.4">
+      <c r="E100" s="34"/>
+    </row>
+    <row r="101" spans="5:5" ht="14.4">
+      <c r="E101" s="34"/>
+    </row>
+    <row r="102" spans="5:5" ht="14.4">
+      <c r="E102" s="34"/>
+    </row>
+    <row r="103" spans="5:5" ht="14.4">
+      <c r="E103" s="34"/>
+    </row>
+    <row r="104" spans="5:5" ht="14.4">
+      <c r="E104" s="34"/>
+    </row>
+    <row r="105" spans="5:5" ht="14.4">
+      <c r="E105" s="34"/>
+    </row>
+    <row r="106" spans="5:5" ht="14.4">
+      <c r="E106" s="34"/>
+    </row>
+    <row r="107" spans="5:5" ht="14.4">
+      <c r="E107" s="34"/>
+    </row>
+    <row r="108" spans="5:5" ht="14.4">
+      <c r="E108" s="34"/>
+    </row>
+    <row r="109" spans="5:5" ht="14.4">
+      <c r="E109" s="34"/>
+    </row>
+    <row r="110" spans="5:5" ht="14.4">
+      <c r="E110" s="34"/>
+    </row>
+    <row r="111" spans="5:5" ht="14.4">
+      <c r="E111" s="34"/>
+    </row>
+    <row r="112" spans="5:5" ht="14.4">
+      <c r="E112" s="34"/>
+    </row>
+    <row r="113" spans="5:5" ht="14.4">
+      <c r="E113" s="34"/>
+    </row>
+    <row r="114" spans="5:5" ht="14.4">
+      <c r="E114" s="34"/>
+    </row>
+    <row r="115" spans="5:5" ht="14.4">
+      <c r="E115" s="34"/>
+    </row>
+    <row r="116" spans="5:5" ht="14.4">
+      <c r="E116" s="34"/>
+    </row>
+    <row r="117" spans="5:5" ht="14.4">
+      <c r="E117" s="34"/>
+    </row>
+    <row r="118" spans="5:5" ht="14.4">
+      <c r="E118" s="34"/>
+    </row>
+    <row r="119" spans="5:5" ht="14.4">
+      <c r="E119" s="34"/>
+    </row>
+    <row r="120" spans="5:5" ht="14.4">
+      <c r="E120" s="34"/>
+    </row>
+    <row r="121" spans="5:5" ht="14.4">
+      <c r="E121" s="34"/>
+    </row>
+    <row r="122" spans="5:5" ht="14.4">
+      <c r="E122" s="34"/>
+    </row>
+    <row r="123" spans="5:5" ht="14.4">
+      <c r="E123" s="34"/>
+    </row>
+    <row r="124" spans="5:5" ht="14.4">
+      <c r="E124" s="34"/>
+    </row>
+    <row r="125" spans="5:5" ht="14.4">
+      <c r="E125" s="34"/>
+    </row>
+    <row r="126" spans="5:5" ht="14.4">
+      <c r="E126" s="34"/>
+    </row>
+    <row r="127" spans="5:5" ht="14.4">
+      <c r="E127" s="34"/>
+    </row>
+    <row r="128" spans="5:5" ht="14.4">
+      <c r="E128" s="34"/>
+    </row>
+    <row r="129" spans="5:5" ht="14.4">
+      <c r="E129" s="34"/>
+    </row>
+    <row r="130" spans="5:5" ht="14.4">
+      <c r="E130" s="34"/>
+    </row>
+    <row r="131" spans="5:5" ht="14.4">
+      <c r="E131" s="34"/>
+    </row>
+    <row r="132" spans="5:5" ht="14.4">
+      <c r="E132" s="34"/>
+    </row>
+    <row r="133" spans="5:5" ht="14.4">
+      <c r="E133" s="34"/>
+    </row>
+    <row r="134" spans="5:5" ht="14.4">
+      <c r="E134" s="34"/>
+    </row>
+    <row r="135" spans="5:5" ht="14.4">
+      <c r="E135" s="34"/>
+    </row>
+    <row r="136" spans="5:5" ht="14.4">
+      <c r="E136" s="34"/>
+    </row>
+    <row r="137" spans="5:5" ht="14.4">
+      <c r="E137" s="34"/>
+    </row>
+    <row r="138" spans="5:5" ht="14.4">
+      <c r="E138" s="34"/>
+    </row>
+    <row r="139" spans="5:5" ht="14.4">
+      <c r="E139" s="34"/>
+    </row>
+    <row r="140" spans="5:5" ht="14.4">
+      <c r="E140" s="34"/>
+    </row>
+    <row r="141" spans="5:5" ht="14.4">
+      <c r="E141" s="34"/>
+    </row>
+    <row r="142" spans="5:5" ht="14.4">
+      <c r="E142" s="34"/>
+    </row>
+    <row r="143" spans="5:5" ht="14.4">
+      <c r="E143" s="34"/>
+    </row>
+    <row r="144" spans="5:5" ht="14.4">
+      <c r="E144" s="34"/>
+    </row>
+    <row r="145" spans="5:5" ht="14.4">
+      <c r="E145" s="34"/>
+    </row>
+    <row r="146" spans="5:5" ht="14.4">
+      <c r="E146" s="34"/>
+    </row>
+    <row r="147" spans="5:5" ht="14.4">
+      <c r="E147" s="34"/>
+    </row>
+    <row r="148" spans="5:5" ht="14.4">
+      <c r="E148" s="34"/>
+    </row>
+    <row r="149" spans="5:5" ht="14.4">
+      <c r="E149" s="34"/>
+    </row>
+    <row r="150" spans="5:5" ht="14.4">
+      <c r="E150" s="34"/>
+    </row>
+    <row r="151" spans="5:5" ht="14.4">
+      <c r="E151" s="34"/>
+    </row>
+    <row r="152" spans="5:5" ht="14.4">
+      <c r="E152" s="34"/>
+    </row>
+    <row r="153" spans="5:5" ht="14.4">
+      <c r="E153" s="34"/>
+    </row>
+    <row r="154" spans="5:5" ht="14.4">
+      <c r="E154" s="34"/>
+    </row>
+    <row r="155" spans="5:5" ht="14.4">
+      <c r="E155" s="34"/>
+    </row>
+    <row r="156" spans="5:5" ht="14.4">
+      <c r="E156" s="34"/>
+    </row>
+    <row r="157" spans="5:5" ht="14.4">
+      <c r="E157" s="34"/>
+    </row>
+    <row r="158" spans="5:5" ht="14.4">
+      <c r="E158" s="34"/>
+    </row>
+    <row r="159" spans="5:5" ht="14.4">
+      <c r="E159" s="34"/>
+    </row>
+    <row r="160" spans="5:5" ht="14.4">
+      <c r="E160" s="34"/>
+    </row>
+    <row r="161" spans="5:5" ht="14.4">
+      <c r="E161" s="34"/>
+    </row>
+    <row r="162" spans="5:5" ht="14.4">
+      <c r="E162" s="34"/>
+    </row>
+    <row r="163" spans="5:5" ht="14.4">
+      <c r="E163" s="34"/>
+    </row>
+    <row r="164" spans="5:5" ht="14.4">
+      <c r="E164" s="34"/>
+    </row>
+    <row r="165" spans="5:5" ht="14.4">
+      <c r="E165" s="34"/>
+    </row>
+    <row r="166" spans="5:5" ht="14.4">
+      <c r="E166" s="34"/>
+    </row>
+    <row r="167" spans="5:5" ht="14.4">
+      <c r="E167" s="34"/>
+    </row>
+    <row r="168" spans="5:5" ht="14.4">
+      <c r="E168" s="34"/>
+    </row>
+    <row r="169" spans="5:5" ht="14.4">
+      <c r="E169" s="34"/>
+    </row>
+    <row r="170" spans="5:5" ht="14.4">
+      <c r="E170" s="34"/>
+    </row>
+    <row r="171" spans="5:5" ht="14.4">
+      <c r="E171" s="34"/>
+    </row>
+    <row r="172" spans="5:5" ht="14.4">
+      <c r="E172" s="34"/>
+    </row>
+    <row r="173" spans="5:5" ht="14.4">
+      <c r="E173" s="34"/>
+    </row>
+    <row r="174" spans="5:5" ht="14.4">
+      <c r="E174" s="34"/>
+    </row>
+    <row r="175" spans="5:5" ht="14.4">
+      <c r="E175" s="34"/>
+    </row>
+    <row r="176" spans="5:5" ht="14.4">
+      <c r="E176" s="34"/>
+    </row>
+    <row r="177" spans="5:5" ht="14.4">
+      <c r="E177" s="34"/>
+    </row>
+    <row r="178" spans="5:5" ht="14.4">
+      <c r="E178" s="34"/>
+    </row>
+    <row r="179" spans="5:5" ht="14.4">
+      <c r="E179" s="34"/>
+    </row>
+    <row r="180" spans="5:5" ht="14.4">
+      <c r="E180" s="34"/>
+    </row>
+    <row r="181" spans="5:5" ht="14.4">
+      <c r="E181" s="34"/>
+    </row>
+    <row r="182" spans="5:5" ht="14.4">
+      <c r="E182" s="34"/>
+    </row>
+    <row r="183" spans="5:5" ht="14.4">
+      <c r="E183" s="34"/>
+    </row>
+    <row r="184" spans="5:5" ht="14.4">
+      <c r="E184" s="34"/>
+    </row>
+    <row r="185" spans="5:5" ht="14.4">
+      <c r="E185" s="34"/>
+    </row>
+    <row r="186" spans="5:5" ht="14.4">
+      <c r="E186" s="34"/>
+    </row>
+    <row r="187" spans="5:5" ht="14.4">
+      <c r="E187" s="34"/>
+    </row>
+    <row r="188" spans="5:5" ht="14.4">
+      <c r="E188" s="34"/>
+    </row>
+    <row r="189" spans="5:5" ht="14.4">
+      <c r="E189" s="34"/>
+    </row>
+    <row r="190" spans="5:5" ht="14.4">
+      <c r="E190" s="34"/>
+    </row>
+    <row r="191" spans="5:5" ht="14.4">
+      <c r="E191" s="34"/>
+    </row>
+    <row r="192" spans="5:5" ht="14.4">
+      <c r="E192" s="34"/>
+    </row>
+    <row r="193" spans="5:5" ht="14.4">
+      <c r="E193" s="34"/>
+    </row>
+    <row r="194" spans="5:5" ht="14.4">
+      <c r="E194" s="34"/>
+    </row>
+    <row r="195" spans="5:5" ht="14.4">
+      <c r="E195" s="34"/>
+    </row>
+    <row r="196" spans="5:5" ht="14.4">
+      <c r="E196" s="34"/>
+    </row>
+    <row r="197" spans="5:5" ht="14.4">
+      <c r="E197" s="34"/>
+    </row>
+    <row r="198" spans="5:5" ht="14.4">
+      <c r="E198" s="34"/>
+    </row>
+    <row r="199" spans="5:5" ht="14.4">
+      <c r="E199" s="34"/>
+    </row>
+    <row r="200" spans="5:5" ht="14.4">
+      <c r="E200" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="11">
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -2332,7 +3093,7 @@
     <col min="10" max="16384" width="10.33203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.15" customHeight="1">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -7133,620 +7894,620 @@
     <col min="12" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" customHeight="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:11" ht="19.2" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.35" customHeight="1">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+    </row>
+    <row r="2" spans="1:11" ht="17.850000000000001" customHeight="1">
+      <c r="A2" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="39"/>
-      <c r="E3" s="43" t="s">
+      <c r="D3" s="36"/>
+      <c r="E3" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="13" t="s">
+      <c r="F3" s="36"/>
+      <c r="G3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="1:11" ht="20.85" customHeight="1">
-      <c r="A4" s="14" t="s">
+      <c r="I3" s="36"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="16.649999999999999" customHeight="1">
+      <c r="A4" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A5" s="16">
+    <row r="5" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A5" s="12">
         <v>46235</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="13">
         <v>124.3</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13">
         <v>176.16</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="13">
         <v>1015.83</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="13">
         <v>8400</v>
       </c>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="18">
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="14">
         <v>9716.2900000000009</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A6" s="20">
+    <row r="6" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A6" s="16">
         <v>46236</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="18">
-        <v>0</v>
-      </c>
-      <c r="K6" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A7" s="16">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="14">
+        <v>0</v>
+      </c>
+      <c r="K6" s="18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A7" s="12">
         <v>46237</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="13">
         <v>333.35</v>
       </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13">
         <v>508.93</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17">
+      <c r="E7" s="13"/>
+      <c r="F7" s="13">
         <v>940.8</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="13">
         <v>560.48</v>
       </c>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="18">
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="14">
         <v>2343.56</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A8" s="20">
+    <row r="8" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A8" s="16">
         <v>46238</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="17">
         <v>1929.79</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="17">
         <v>985.6</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="17">
         <v>160</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="17">
         <v>827.16</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="17">
         <v>211.31</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="17">
         <v>57.63</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="17">
         <v>124.3</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="18">
+      <c r="I8" s="17"/>
+      <c r="J8" s="14">
         <v>4295.79</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="18">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A9" s="16">
+    <row r="9" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A9" s="12">
         <v>46239</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="13">
         <v>197.75</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13">
         <v>100</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="13">
         <v>45.2</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="13">
         <v>824.9</v>
       </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17">
+      <c r="G9" s="13"/>
+      <c r="H9" s="13">
         <v>335.61</v>
       </c>
-      <c r="I9" s="17"/>
-      <c r="J9" s="18">
+      <c r="I9" s="13"/>
+      <c r="J9" s="14">
         <v>1503.46</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="15">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A10" s="20">
+    <row r="10" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A10" s="16">
         <v>46240</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="17">
         <v>622.82000000000005</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="18">
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="14">
         <v>622.82000000000005</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A11" s="16">
+    <row r="11" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A11" s="12">
         <v>46241</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="13">
         <v>1115.8800000000001</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="13">
         <v>67.8</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="13">
         <v>461.98</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="13">
         <v>1021.92</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17">
+      <c r="F11" s="13"/>
+      <c r="G11" s="13">
         <v>76.84</v>
       </c>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17">
+      <c r="H11" s="13"/>
+      <c r="I11" s="13">
         <v>22.02</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="14">
         <v>2766.44</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A12" s="20">
+    <row r="12" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A12" s="16">
         <v>46242</v>
       </c>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17">
         <v>814.73</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="18">
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="14">
         <v>814.73</v>
       </c>
-      <c r="K12" s="22">
+      <c r="K12" s="18">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A13" s="16">
+    <row r="13" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A13" s="12">
         <v>46243</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="18">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A14" s="20">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="14">
+        <v>0</v>
+      </c>
+      <c r="K13" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A14" s="16">
         <v>46244</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="17">
         <v>716.42</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="17">
         <v>113.14</v>
       </c>
-      <c r="D14" s="21">
+      <c r="D14" s="17">
         <v>267.26</v>
       </c>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21">
+      <c r="E14" s="17"/>
+      <c r="F14" s="17">
         <v>911.91</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="17">
         <v>554.83000000000004</v>
       </c>
-      <c r="H14" s="21">
+      <c r="H14" s="17">
         <v>192.1</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="17">
         <v>79.89</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="14">
         <v>2835.55</v>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="18">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A15" s="16">
+    <row r="15" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A15" s="12">
         <v>46245</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="13">
         <v>904</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="13">
         <v>372.9</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="13">
         <v>604.79999999999995</v>
       </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
+      <c r="E15" s="13">
+        <v>0</v>
+      </c>
+      <c r="F15" s="13">
         <v>225.25</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="13">
         <v>552.16</v>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="13">
         <v>30319</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="18">
+      <c r="I15" s="13"/>
+      <c r="J15" s="14">
         <v>32978.11</v>
       </c>
-      <c r="K15" s="19">
+      <c r="K15" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A16" s="20">
+    <row r="16" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A16" s="16">
         <v>46246</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="17">
         <v>6110.3</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17">
         <v>729.98</v>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="17">
         <v>640.59</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16" s="17">
         <v>281.29000000000002</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="17">
         <v>56.5</v>
       </c>
-      <c r="H16" s="21">
+      <c r="H16" s="17">
         <v>544.59</v>
       </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="18">
+      <c r="I16" s="17"/>
+      <c r="J16" s="14">
         <v>8363.25</v>
       </c>
-      <c r="K16" s="22">
+      <c r="K16" s="18">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A17" s="16">
+    <row r="17" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A17" s="12">
         <v>46247</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="13">
         <v>604.86</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="13">
         <v>1.38</v>
       </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17">
+      <c r="D17" s="13"/>
+      <c r="E17" s="13">
         <v>169.3</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="13">
         <v>564.08000000000004</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="13">
         <v>1681.24</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="13">
         <v>216.96</v>
       </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="18">
+      <c r="I17" s="13"/>
+      <c r="J17" s="14">
         <v>3237.82</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A18" s="20">
+    <row r="18" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A18" s="16">
         <v>46248</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="17">
         <v>9077.44</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="17">
         <v>66.67</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="17">
         <v>25.99</v>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="17">
         <v>1893.46</v>
       </c>
-      <c r="F18" s="21">
-        <v>0</v>
-      </c>
-      <c r="G18" s="21">
+      <c r="F18" s="17">
+        <v>0</v>
+      </c>
+      <c r="G18" s="17">
         <v>335.61</v>
       </c>
-      <c r="H18" s="21">
-        <v>0</v>
-      </c>
-      <c r="I18" s="21"/>
-      <c r="J18" s="18">
+      <c r="H18" s="17">
+        <v>0</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="14">
         <v>11399.17</v>
       </c>
-      <c r="K18" s="22">
+      <c r="K18" s="18">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A19" s="16">
+    <row r="19" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A19" s="12">
         <v>46249</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17">
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13">
         <v>532.23</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="13">
         <v>40.99</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="13">
         <v>84.75</v>
       </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17">
+      <c r="G19" s="13"/>
+      <c r="H19" s="13">
         <v>244.08</v>
       </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="18">
+      <c r="I19" s="13"/>
+      <c r="J19" s="14">
         <v>902.05</v>
       </c>
-      <c r="K19" s="19">
+      <c r="K19" s="15">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A20" s="20">
+    <row r="20" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A20" s="16">
         <v>46250</v>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="17">
         <v>282.5</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21">
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17">
         <v>237.34</v>
       </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="18">
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="14">
         <v>519.84</v>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="18">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A21" s="16">
+    <row r="21" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A21" s="12">
         <v>46251</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="13">
         <v>387.59</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="13">
         <v>21.47</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="13">
         <v>793.26</v>
       </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17">
+      <c r="E21" s="13"/>
+      <c r="F21" s="13">
         <v>637.25</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="13">
         <v>966.05</v>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="13">
         <v>728.06</v>
       </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="18">
+      <c r="I21" s="13"/>
+      <c r="J21" s="14">
         <v>3533.68</v>
       </c>
-      <c r="K21" s="19">
+      <c r="K21" s="15">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A22" s="20">
+    <row r="22" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A22" s="16">
         <v>46252</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="17">
         <v>1671.29</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="17">
         <v>6163.5</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="17">
         <v>339</v>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="17">
         <v>307.38</v>
       </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21">
+      <c r="F22" s="17"/>
+      <c r="G22" s="17">
         <v>310.24</v>
       </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="18">
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="14">
         <v>8791.41</v>
       </c>
-      <c r="K22" s="22">
+      <c r="K22" s="18">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16.8" customHeight="1">
-      <c r="A23" s="16">
+    <row r="23" spans="1:11" ht="13.35" customHeight="1">
+      <c r="A23" s="12">
         <v>46253</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="13">
         <v>371.77</v>
       </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17">
+      <c r="C23" s="13"/>
+      <c r="D23" s="13">
         <v>56.5</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="13">
         <v>2093.02</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="13">
         <v>5251.38</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="13">
         <v>485.25</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="18">
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="14">
         <v>8257.92</v>
       </c>
-      <c r="K23" s="19">
+      <c r="K23" s="15">
         <v>5</v>
       </c>
     </row>
@@ -7780,771 +8541,789 @@
     <col min="26" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="25.65" customHeight="1">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:25" ht="20.55" customHeight="1">
+      <c r="A1" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="X1" s="23" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="X1" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="Y1" s="33" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="22.35" customHeight="1">
-      <c r="A2" s="42" t="s">
+    <row r="2" spans="1:25" ht="17.850000000000001" customHeight="1">
+      <c r="A2" s="39" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="X2" s="23" t="s">
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="X2" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="Y2" s="37">
+      <c r="Y2" s="33">
         <f t="shared" ref="Y2:Y20" si="0">B15</f>
         <v>9716.2900000000009</v>
       </c>
     </row>
     <row r="3" spans="1:25">
-      <c r="X3" s="23" t="s">
+      <c r="X3" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="Y3" s="37">
+      <c r="Y3" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:25" ht="12" customHeight="1">
+      <c r="A4" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14" t="s">
+      <c r="F4" s="10"/>
+      <c r="G4" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="X4" s="23" t="s">
+      <c r="H4" s="10"/>
+      <c r="X4" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="Y4" s="37">
+      <c r="Y4" s="33">
         <f t="shared" si="0"/>
         <v>2343.56</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="12" customHeight="1">
-      <c r="A5" s="49">
+    <row r="5" spans="1:25" ht="26.4" customHeight="1">
+      <c r="A5" s="44">
         <v>46235</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="49">
+      <c r="B5" s="36"/>
+      <c r="C5" s="44">
         <v>46253</v>
       </c>
-      <c r="D5" s="39"/>
-      <c r="E5" s="50" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="45" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="39"/>
-      <c r="G5" s="51" t="s">
+      <c r="F5" s="36"/>
+      <c r="G5" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="H5" s="39"/>
-      <c r="X5" s="23" t="s">
+      <c r="H5" s="36"/>
+      <c r="X5" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="Y5" s="37">
+      <c r="Y5" s="33">
         <f t="shared" si="0"/>
         <v>4295.79</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="X6" s="23" t="s">
+      <c r="X6" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="Y6" s="37">
+      <c r="Y6" s="33">
         <f t="shared" si="0"/>
         <v>1503.46</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="14.4">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13" t="s">
+      <c r="B7" s="9"/>
+      <c r="C7" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13" t="s">
+      <c r="D7" s="9"/>
+      <c r="E7" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="9"/>
+      <c r="G7" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="53" t="s">
-        <v>330</v>
-      </c>
-      <c r="J7" s="53"/>
-      <c r="X7" s="23" t="s">
+      <c r="H7" s="9"/>
+      <c r="I7" s="41" t="s">
+        <v>332</v>
+      </c>
+      <c r="J7" s="41"/>
+      <c r="K7" s="52" t="s">
+        <v>333</v>
+      </c>
+      <c r="L7" s="52"/>
+      <c r="X7" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="Y7" s="37">
+      <c r="Y7" s="33">
         <f t="shared" si="0"/>
         <v>622.82000000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="15.6" customHeight="1">
-      <c r="A8" s="44">
+    <row r="8" spans="1:25" ht="16.2" customHeight="1">
+      <c r="A8" s="47">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="44">
+      <c r="B8" s="48"/>
+      <c r="C8" s="47">
         <f>IFERROR(AVERAGEIF(H15:H22,"&gt;0"),0)</f>
         <v>12860.23625</v>
       </c>
-      <c r="D8" s="45"/>
-      <c r="E8" s="44">
+      <c r="D8" s="48"/>
+      <c r="E8" s="47">
         <f>IFERROR(MAX(H15:H22),0)</f>
         <v>32704.7</v>
       </c>
-      <c r="F8" s="45"/>
-      <c r="G8" s="46">
+      <c r="F8" s="48"/>
+      <c r="G8" s="49">
         <f>COUNTIF(H15:H22,"&gt;0")</f>
         <v>8</v>
       </c>
-      <c r="H8" s="47"/>
-      <c r="I8" s="54">
-        <f>IF($E$5&lt;&gt;"TODAS",SUMIF('SALDOS POR CUENTA'!$B$5:$B$100,$E$5,'SALDOS POR CUENTA'!$D$5:$D$100),IF($G$5&lt;&gt;"TODOS",SUMIF('SALDOS POR CUENTA'!$A$5:$A$100,"*"&amp;SUBSTITUTE(TRIM($G$5),"BANCO ","")&amp;"*",'SALDOS POR CUENTA'!$D$5:$D$100),SUM('SALDOS POR CUENTA'!$D$5:$D$100)))</f>
+      <c r="H8" s="50"/>
+      <c r="I8" s="42">
+        <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$D$5:$D$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$D$5:$D$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$D$5:$D$200),0)))</f>
         <v>268945.52</v>
       </c>
-      <c r="J8" s="54"/>
-      <c r="X8" s="23" t="s">
+      <c r="J8" s="42"/>
+      <c r="K8" s="53">
+        <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$E$5:$E$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$E$5:$E$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$E$5:$E$200),0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="53"/>
+      <c r="X8" s="19" t="s">
         <v>310</v>
       </c>
-      <c r="Y8" s="37">
+      <c r="Y8" s="33">
         <f t="shared" si="0"/>
         <v>2766.44</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="X9" s="23" t="s">
+      <c r="X9" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="Y9" s="37">
+      <c r="Y9" s="33">
         <f t="shared" si="0"/>
         <v>814.73</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="6.45" customHeight="1">
-      <c r="A10" s="24"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="X10" s="23" t="s">
+    <row r="10" spans="1:25" ht="5.0999999999999996" customHeight="1">
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="X10" s="19" t="s">
         <v>312</v>
       </c>
-      <c r="Y10" s="37">
+      <c r="Y10" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:25">
-      <c r="X11" s="23" t="s">
+      <c r="X11" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="Y11" s="37">
+      <c r="Y11" s="33">
         <f t="shared" si="0"/>
         <v>2835.55</v>
       </c>
     </row>
     <row r="12" spans="1:25">
-      <c r="X12" s="23" t="s">
+      <c r="X12" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="Y12" s="37">
+      <c r="Y12" s="33">
         <f t="shared" si="0"/>
         <v>32978.11</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="12" customHeight="1">
-      <c r="A13" s="48" t="s">
+    <row r="13" spans="1:25" ht="9.6" customHeight="1">
+      <c r="A13" s="51" t="s">
         <v>315</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="F13" s="48" t="s">
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="F13" s="51" t="s">
         <v>316</v>
       </c>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="X13" s="23" t="s">
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="X13" s="19" t="s">
         <v>317</v>
       </c>
-      <c r="Y13" s="37">
+      <c r="Y13" s="33">
         <f t="shared" si="0"/>
         <v>8363.25</v>
       </c>
     </row>
     <row r="14" spans="1:25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="X14" s="23" t="s">
+      <c r="X14" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="Y14" s="37">
+      <c r="Y14" s="33">
         <f t="shared" si="0"/>
         <v>3237.82</v>
       </c>
     </row>
     <row r="15" spans="1:25">
-      <c r="A15" s="25">
+      <c r="A15" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A5&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A5&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A5,"")</f>
         <v>46235</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="31">
         <f>IF(A15="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A15,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A15,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>9716.2900000000009</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="31">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="22">
         <f>IF(A15="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A15,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B15&gt;0,1,0)))</f>
         <v>4</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="G15" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="35">
+      <c r="H15" s="31">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F15)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G15,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$B$5:$B$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>24450.060000000005</v>
       </c>
-      <c r="X15" s="23" t="s">
+      <c r="X15" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="Y15" s="37">
+      <c r="Y15" s="33">
         <f t="shared" si="0"/>
         <v>11399.17</v>
       </c>
     </row>
     <row r="16" spans="1:25">
-      <c r="A16" s="29">
+      <c r="A16" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A6&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A6&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A6,"")</f>
         <v>46236</v>
       </c>
-      <c r="B16" s="36">
+      <c r="B16" s="32">
         <f>IF(A16="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A16,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A16,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>0</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="32">
         <f t="shared" ref="C16:C33" si="1">B16-B15</f>
         <v>-9716.2900000000009</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="26">
         <f>IF(A16="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A16,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B16&gt;0,1,0)))</f>
         <v>0</v>
       </c>
-      <c r="F16" s="31" t="s">
+      <c r="F16" s="27" t="s">
         <v>289</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="36">
+      <c r="H16" s="32">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F16)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G16,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$C$5:$C$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>7792.46</v>
       </c>
-      <c r="X16" s="23" t="s">
+      <c r="X16" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="Y16" s="37">
+      <c r="Y16" s="33">
         <f t="shared" si="0"/>
         <v>902.05</v>
       </c>
     </row>
     <row r="17" spans="1:25">
-      <c r="A17" s="25">
+      <c r="A17" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A7&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A7&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A7,"")</f>
         <v>46237</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="31">
         <f>IF(A17="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A17,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A17,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>2343.56</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="31">
         <f t="shared" si="1"/>
         <v>2343.56</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="22">
         <f>IF(A17="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A17,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B17&gt;0,1,0)))</f>
         <v>4</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="35">
+      <c r="H17" s="31">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F17)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G17,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$D$5:$D$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>4756.09</v>
       </c>
-      <c r="X17" s="23" t="s">
+      <c r="X17" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="Y17" s="37">
+      <c r="Y17" s="33">
         <f t="shared" si="0"/>
         <v>519.84</v>
       </c>
     </row>
     <row r="18" spans="1:25">
-      <c r="A18" s="29">
+      <c r="A18" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A8&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A8&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A8,"")</f>
         <v>46238</v>
       </c>
-      <c r="B18" s="36">
+      <c r="B18" s="32">
         <f>IF(A18="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A18,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A18,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>4295.79</v>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="32">
         <f t="shared" si="1"/>
         <v>1952.23</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="26">
         <f>IF(A18="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A18,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B18&gt;0,1,0)))</f>
         <v>7</v>
       </c>
-      <c r="F18" s="31" t="s">
+      <c r="F18" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="H18" s="36">
+      <c r="H18" s="32">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F18)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G18,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$E$5:$E$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>9106.92</v>
       </c>
-      <c r="X18" s="23" t="s">
+      <c r="X18" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="Y18" s="37">
+      <c r="Y18" s="33">
         <f t="shared" si="0"/>
         <v>3533.68</v>
       </c>
     </row>
     <row r="19" spans="1:25">
-      <c r="A19" s="25">
+      <c r="A19" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A9&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A9&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A9,"")</f>
         <v>46239</v>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="31">
         <f>IF(A19="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A19,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A19,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>1503.46</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="31">
         <f t="shared" si="1"/>
         <v>-2792.33</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="22">
         <f>IF(A19="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A19,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B19&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="31">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F19)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G19,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$F$5:$F$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>18332.919999999998</v>
       </c>
-      <c r="X19" s="23" t="s">
+      <c r="X19" s="19" t="s">
         <v>327</v>
       </c>
-      <c r="Y19" s="37">
+      <c r="Y19" s="33">
         <f t="shared" si="0"/>
         <v>8791.41</v>
       </c>
     </row>
     <row r="20" spans="1:25">
-      <c r="A20" s="29">
+      <c r="A20" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A10&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A10&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A10,"")</f>
         <v>46240</v>
       </c>
-      <c r="B20" s="36">
+      <c r="B20" s="32">
         <f>IF(A20="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A20,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A20,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>622.82000000000005</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="32">
         <f t="shared" si="1"/>
         <v>-880.64</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="26">
         <f>IF(A20="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A20,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B20&gt;0,1,0)))</f>
         <v>1</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="36">
+      <c r="H20" s="32">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F20)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G20,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$G$5:$G$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>5636.83</v>
       </c>
-      <c r="X20" s="23" t="s">
+      <c r="X20" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="Y20" s="37">
+      <c r="Y20" s="33">
         <f t="shared" si="0"/>
         <v>8257.92</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="14.4">
-      <c r="A21" s="25">
+      <c r="A21" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A11&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A11&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A11,"")</f>
         <v>46241</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="31">
         <f>IF(A21="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A21,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A21,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>2766.44</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="31">
         <f t="shared" si="1"/>
         <v>2143.62</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="22">
         <f>IF(A21="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A21,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B21&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-      <c r="F21" s="27" t="s">
+      <c r="F21" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="G21" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="31">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F21)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G21,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$H$5:$H$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>32704.7</v>
       </c>
-      <c r="Y21" s="33"/>
+      <c r="Y21" s="29"/>
     </row>
     <row r="22" spans="1:25" ht="14.4">
-      <c r="A22" s="29">
+      <c r="A22" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A12&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A12&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A12,"")</f>
         <v>46242</v>
       </c>
-      <c r="B22" s="36">
+      <c r="B22" s="32">
         <f>IF(A22="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A22,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A22,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>814.73</v>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="32">
         <f t="shared" si="1"/>
         <v>-1951.71</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="26">
         <f>IF(A22="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A22,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B22&gt;0,1,0)))</f>
         <v>1</v>
       </c>
-      <c r="F22" s="31" t="s">
+      <c r="F22" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H22" s="36">
+      <c r="H22" s="32">
         <f>IF(AND(OR($G$5="TODOS",TRIM($G$5)=TRIM(F22)),OR($E$5="TODAS",TEXT($E$5,"0")=TEXT(G22,"0"))),SUMIFS('REPORTE CREDITOS DIARIOS'!$I$5:$I$23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&gt;="&amp;$A$5,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,"&lt;="&amp;$C$5),0)</f>
         <v>101.91</v>
       </c>
-      <c r="Y22" s="33"/>
+      <c r="Y22" s="29"/>
     </row>
     <row r="23" spans="1:25" ht="14.4">
-      <c r="A23" s="25">
+      <c r="A23" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A13&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A13&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A13,"")</f>
         <v>46243</v>
       </c>
-      <c r="B23" s="35">
+      <c r="B23" s="31">
         <f>IF(A23="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A23,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>0</v>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="31">
         <f t="shared" si="1"/>
         <v>-814.73</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="22">
         <f>IF(A23="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B23&gt;0,1,0)))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="52" t="s">
-        <v>331</v>
-      </c>
-      <c r="G23" s="52"/>
-      <c r="H23" s="34">
+      <c r="F23" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="G23" s="43"/>
+      <c r="H23" s="30">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
       </c>
-      <c r="Y23" s="33"/>
+      <c r="Y23" s="29"/>
     </row>
     <row r="24" spans="1:25" ht="14.4">
-      <c r="A24" s="29">
+      <c r="A24" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A14&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A14&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A14,"")</f>
         <v>46244</v>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="32">
         <f>IF(A24="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A24,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A24,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>2835.55</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="32">
         <f t="shared" si="1"/>
         <v>2835.55</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="26">
         <f>IF(A24="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A24,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B24&gt;0,1,0)))</f>
         <v>7</v>
       </c>
-      <c r="Y24" s="33"/>
+      <c r="Y24" s="29"/>
     </row>
     <row r="25" spans="1:25" ht="14.4">
-      <c r="A25" s="25">
+      <c r="A25" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A15&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A15&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A15,"")</f>
         <v>46245</v>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="31">
         <f>IF(A25="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A25,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A25,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>32978.11</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="31">
         <f t="shared" si="1"/>
         <v>30142.560000000001</v>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="22">
         <f>IF(A25="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A25,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B25&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-      <c r="Y25" s="33"/>
+      <c r="Y25" s="29"/>
     </row>
     <row r="26" spans="1:25" ht="14.4">
-      <c r="A26" s="29">
+      <c r="A26" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A16&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A16&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A16,"")</f>
         <v>46246</v>
       </c>
-      <c r="B26" s="36">
+      <c r="B26" s="32">
         <f>IF(A26="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A26,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A26,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>8363.25</v>
       </c>
-      <c r="C26" s="36">
+      <c r="C26" s="32">
         <f t="shared" si="1"/>
         <v>-24614.86</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="26">
         <f>IF(A26="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A26,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B26&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-      <c r="Y26" s="33"/>
+      <c r="Y26" s="29"/>
     </row>
     <row r="27" spans="1:25" ht="14.4">
-      <c r="A27" s="25">
+      <c r="A27" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A17&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A17&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A17,"")</f>
         <v>46247</v>
       </c>
-      <c r="B27" s="35">
+      <c r="B27" s="31">
         <f>IF(A27="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A27,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A27,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>3237.82</v>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="31">
         <f t="shared" si="1"/>
         <v>-5125.43</v>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="22">
         <f>IF(A27="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A27,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B27&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-      <c r="Y27" s="33"/>
+      <c r="Y27" s="29"/>
     </row>
     <row r="28" spans="1:25" ht="14.4">
-      <c r="A28" s="29">
+      <c r="A28" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A18&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A18&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A18,"")</f>
         <v>46248</v>
       </c>
-      <c r="B28" s="36">
+      <c r="B28" s="32">
         <f>IF(A28="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A28,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A28,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>11399.17</v>
       </c>
-      <c r="C28" s="36">
+      <c r="C28" s="32">
         <f t="shared" si="1"/>
         <v>8161.35</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="26">
         <f>IF(A28="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A28,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B28&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-      <c r="Y28" s="33"/>
+      <c r="Y28" s="29"/>
     </row>
     <row r="29" spans="1:25" ht="14.4">
-      <c r="A29" s="25">
+      <c r="A29" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A19&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A19&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A19,"")</f>
         <v>46249</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="31">
         <f>IF(A29="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A29,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A29,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>902.05</v>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="31">
         <f t="shared" si="1"/>
         <v>-10497.12</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D29" s="22">
         <f>IF(A29="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A29,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B29&gt;0,1,0)))</f>
         <v>4</v>
       </c>
-      <c r="Y29" s="33"/>
+      <c r="Y29" s="29"/>
     </row>
     <row r="30" spans="1:25" ht="14.4">
-      <c r="A30" s="29">
+      <c r="A30" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A20&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A20&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A20,"")</f>
         <v>46250</v>
       </c>
-      <c r="B30" s="36">
+      <c r="B30" s="32">
         <f>IF(A30="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A30,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A30,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>519.84</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="32">
         <f t="shared" si="1"/>
         <v>-382.20999999999992</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="26">
         <f>IF(A30="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A30,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B30&gt;0,1,0)))</f>
         <v>2</v>
       </c>
-      <c r="Y30" s="33"/>
+      <c r="Y30" s="29"/>
     </row>
     <row r="31" spans="1:25" ht="14.4">
-      <c r="A31" s="25">
+      <c r="A31" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A21&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A21&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A21,"")</f>
         <v>46251</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="31">
         <f>IF(A31="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A31,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A31,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>3533.68</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>3013.8399999999997</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D31" s="22">
         <f>IF(A31="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A31,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B31&gt;0,1,0)))</f>
         <v>6</v>
       </c>
-      <c r="Y31" s="33"/>
+      <c r="Y31" s="29"/>
     </row>
     <row r="32" spans="1:25" ht="14.4">
-      <c r="A32" s="29">
+      <c r="A32" s="25">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A22&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A22&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A22,"")</f>
         <v>46252</v>
       </c>
-      <c r="B32" s="36">
+      <c r="B32" s="32">
         <f>IF(A32="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A32,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A32,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>8791.41</v>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="32">
         <f t="shared" si="1"/>
         <v>5257.73</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="26">
         <f>IF(A32="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A32,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B32&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-      <c r="Y32" s="33"/>
+      <c r="Y32" s="29"/>
     </row>
     <row r="33" spans="1:25" ht="14.4">
-      <c r="A33" s="25">
+      <c r="A33" s="21">
         <f>IF(AND('REPORTE CREDITOS DIARIOS'!A23&gt;=$A$5,'REPORTE CREDITOS DIARIOS'!A23&lt;=$C$5),'REPORTE CREDITOS DIARIOS'!A23,"")</f>
         <v>46253</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="31">
         <f>IF(A33="",0,IF($E$5&lt;&gt;"TODAS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$B$5:$I$23,MATCH(A33,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0),MATCH($E$5,'REPORTE CREDITOS DIARIOS'!$B$4:$I$4,0)),0),IF($G$5="TODOS",IFERROR(SUMIF('REPORTE CREDITOS DIARIOS'!$A$5:$A$23,A33,'REPORTE CREDITOS DIARIOS'!$J$5:$J$23),0),0)))</f>
         <v>8257.92</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>-533.48999999999978</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="22">
         <f>IF(A33="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A33,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B33&gt;0,1,0)))</f>
         <v>5</v>
       </c>
-      <c r="Y33" s="33"/>
+      <c r="Y33" s="29"/>
     </row>
     <row r="34" spans="1:25" ht="14.4">
-      <c r="Y34" s="33"/>
+      <c r="Y34" s="29"/>
     </row>
     <row r="35" spans="1:25" ht="14.4">
-      <c r="A35" s="42" t="s">
-        <v>329</v>
-      </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="Y35" s="33"/>
+      <c r="A35" s="39" t="s">
+        <v>330</v>
+      </c>
+      <c r="B35" s="36"/>
+      <c r="C35" s="36"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36"/>
+      <c r="G35" s="36"/>
+      <c r="H35" s="36"/>
+      <c r="Y35" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F13:H13"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="F23:G23"/>
@@ -8554,13 +9333,6 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F13:H13"/>
   </mergeCells>
   <conditionalFormatting sqref="H15:H22">
     <cfRule type="dataBar" priority="1">

--- a/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
+++ b/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Gonzalez\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-parser\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40780563-218B-40B3-9B54-BB45C6796549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3C7F58-5614-4C23-88A9-2E3A12E77363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="333">
   <si>
     <t>SALDOS INICIALES Y FINALES POR CUENTA</t>
   </si>
@@ -1029,9 +1029,6 @@
   </si>
   <si>
     <t>Nota: el reporte suma únicamente los valores existentes en Crédito / Abono / Valor +. Los movimientos originales permanecen sin cambios.</t>
-  </si>
-  <si>
-    <t>Dinero disponible</t>
   </si>
   <si>
     <t>SALDO FINAL TOTAL</t>
@@ -1053,7 +1050,7 @@
     <numFmt numFmtId="169" formatCode="\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-"/>
     <numFmt numFmtId="170" formatCode="\Q\ #,##0.00;[Red]\-\Q\ #,##0.00"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1167,13 +1164,6 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1294,7 +1284,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1364,21 +1354,38 @@
     <xf numFmtId="169" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="169" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1387,6 +1394,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1398,40 +1408,14 @@
     <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1440,24 +1424,6 @@
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="4" tint="-0.249977111117893"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="-0.249977111117893"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color theme="4" tint="-0.249977111117893"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="4" tint="-0.249977111117893"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1534,6 +1500,24 @@
         <bottom style="thin">
           <color theme="4" tint="-0.249977111117893"/>
         </bottom>
+        <vertical style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </vertical>
+        <horizontal style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="-0.249977111117893"/>
+        </right>
+        <top/>
+        <bottom/>
         <vertical style="thin">
           <color theme="4" tint="-0.249977111117893"/>
         </vertical>
@@ -2114,12 +2098,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SaldosPorCuenta" displayName="SaldosPorCuenta" ref="A4:D12" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SaldosPorCuenta" displayName="SaldosPorCuenta" ref="A4:D12" totalsRowShown="0" headerRowDxfId="4">
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Banco" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cuenta" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Saldo inicial " dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Saldo final " dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Banco" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Cuenta" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Saldo inicial " dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Saldo final " dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2320,7 +2304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:E200"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="27.44140625" style="8" customWidth="1"/>
@@ -2329,178 +2313,158 @@
     <col min="5" max="16384" width="10.33203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-    </row>
-    <row r="2" spans="1:6" ht="17.850000000000001" customHeight="1">
-      <c r="A2" s="37" t="s">
+    <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
+      <c r="A1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+    </row>
+    <row r="2" spans="1:5" ht="17.850000000000001" customHeight="1">
+      <c r="A2" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-    </row>
-    <row r="4" spans="1:6" ht="19.2" customHeight="1">
-      <c r="A4" s="54" t="s">
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+    </row>
+    <row r="4" spans="1:5" ht="19.2" customHeight="1">
+      <c r="A4" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="B4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="54" t="s">
+      <c r="D4" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="55" t="s">
-        <v>331</v>
-      </c>
-      <c r="F4" s="55"/>
-    </row>
-    <row r="5" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A5" s="56" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A5" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="38">
         <v>76663.7</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="38">
         <v>71075.34</v>
       </c>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-    </row>
-    <row r="6" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A6" s="56" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="58">
+      <c r="C6" s="38">
         <v>14148.75</v>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="38">
         <v>21941.21</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-    </row>
-    <row r="7" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A7" s="56" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A7" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="58">
+      <c r="C7" s="38">
         <v>33171.599999999999</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="38">
         <v>28319.18</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
-    </row>
-    <row r="8" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A8" s="56" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A8" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="58">
+      <c r="C8" s="38">
         <v>9086.82</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="38">
         <v>6003.86</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
-    </row>
-    <row r="9" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A9" s="56" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A9" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="58">
+      <c r="C9" s="38">
         <v>80183.38</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="38">
         <v>81910.289999999994</v>
       </c>
-      <c r="E9" s="59"/>
-      <c r="F9" s="59"/>
-    </row>
-    <row r="10" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A10" s="56" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A10" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="58">
+      <c r="C10" s="38">
         <v>51799.49</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="38">
         <v>33700.51</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
-    </row>
-    <row r="11" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A11" s="56" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A11" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="38">
         <v>38443.89</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="38">
         <v>25869.5</v>
       </c>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-    </row>
-    <row r="12" spans="1:6" ht="12.75" customHeight="1">
-      <c r="A12" s="56" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="12.75" customHeight="1">
+      <c r="A12" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="58">
+      <c r="C12" s="38">
         <v>31.71</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="38">
         <v>125.63</v>
       </c>
-      <c r="E12" s="59"/>
-      <c r="F12" s="59"/>
-    </row>
-    <row r="13" spans="1:6" ht="14.4">
+    </row>
+    <row r="13" spans="1:5" ht="14.4">
       <c r="E13" s="34"/>
     </row>
-    <row r="14" spans="1:6" ht="14.4">
+    <row r="14" spans="1:5" ht="14.4">
       <c r="E14" s="34"/>
     </row>
-    <row r="15" spans="1:6" ht="14.4">
+    <row r="15" spans="1:5" ht="14.4">
       <c r="E15" s="34"/>
     </row>
-    <row r="16" spans="1:6" ht="14.4">
+    <row r="16" spans="1:5" ht="14.4">
       <c r="E16" s="34"/>
     </row>
     <row r="17" spans="5:5" ht="14.4">
@@ -3056,18 +3020,9 @@
       <c r="E200" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -7895,34 +7850,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.2" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
     </row>
     <row r="2" spans="1:11" ht="17.850000000000001" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
@@ -7931,21 +7886,21 @@
       <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="57" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="40" t="s">
+      <c r="D3" s="42"/>
+      <c r="E3" s="57" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="36"/>
+      <c r="F3" s="42"/>
       <c r="G3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="57" t="s">
         <v>241</v>
       </c>
-      <c r="I3" s="36"/>
+      <c r="I3" s="42"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
     </row>
@@ -8542,16 +8497,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.55" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="51" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
       <c r="X1" s="19" t="s">
         <v>290</v>
       </c>
@@ -8560,16 +8515,16 @@
       </c>
     </row>
     <row r="2" spans="1:25" ht="17.850000000000001" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
       <c r="X2" s="19" t="s">
         <v>296</v>
       </c>
@@ -8613,22 +8568,22 @@
       </c>
     </row>
     <row r="5" spans="1:25" ht="26.4" customHeight="1">
-      <c r="A5" s="44">
+      <c r="A5" s="52">
         <v>46235</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="44">
+      <c r="B5" s="42"/>
+      <c r="C5" s="52">
         <v>46253</v>
       </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="45" t="s">
+      <c r="D5" s="42"/>
+      <c r="E5" s="53" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="46" t="s">
+      <c r="F5" s="42"/>
+      <c r="G5" s="54" t="s">
         <v>303</v>
       </c>
-      <c r="H5" s="36"/>
+      <c r="H5" s="42"/>
       <c r="X5" s="19" t="s">
         <v>304</v>
       </c>
@@ -8663,14 +8618,14 @@
         <v>292</v>
       </c>
       <c r="H7" s="9"/>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="J7" s="48"/>
+      <c r="K7" s="39" t="s">
         <v>332</v>
       </c>
-      <c r="J7" s="41"/>
-      <c r="K7" s="52" t="s">
-        <v>333</v>
-      </c>
-      <c r="L7" s="52"/>
+      <c r="L7" s="39"/>
       <c r="X7" s="19" t="s">
         <v>309</v>
       </c>
@@ -8680,36 +8635,36 @@
       </c>
     </row>
     <row r="8" spans="1:25" ht="16.2" customHeight="1">
-      <c r="A8" s="47">
+      <c r="A8" s="43">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="47">
+      <c r="B8" s="44"/>
+      <c r="C8" s="43">
         <f>IFERROR(AVERAGEIF(H15:H22,"&gt;0"),0)</f>
         <v>12860.23625</v>
       </c>
-      <c r="D8" s="48"/>
-      <c r="E8" s="47">
+      <c r="D8" s="44"/>
+      <c r="E8" s="43">
         <f>IFERROR(MAX(H15:H22),0)</f>
         <v>32704.7</v>
       </c>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49">
+      <c r="F8" s="44"/>
+      <c r="G8" s="45">
         <f>COUNTIF(H15:H22,"&gt;0")</f>
         <v>8</v>
       </c>
-      <c r="H8" s="50"/>
-      <c r="I8" s="42">
+      <c r="H8" s="46"/>
+      <c r="I8" s="49">
         <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$D$5:$D$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$D$5:$D$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$D$5:$D$200),0)))</f>
         <v>268945.52</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="53">
-        <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$E$5:$E$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$E$5:$E$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$E$5:$E$200),0)))</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="53"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="40">
+        <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$E$13:$E$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$E$13:$E$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$E$13:$E$200),0)))</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="40"/>
       <c r="X8" s="19" t="s">
         <v>310</v>
       </c>
@@ -8763,17 +8718,17 @@
       </c>
     </row>
     <row r="13" spans="1:25" ht="9.6" customHeight="1">
-      <c r="A13" s="51" t="s">
+      <c r="A13" s="47" t="s">
         <v>315</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="F13" s="51" t="s">
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="F13" s="47" t="s">
         <v>316</v>
       </c>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
       <c r="X13" s="19" t="s">
         <v>317</v>
       </c>
@@ -9097,10 +9052,10 @@
         <f>IF(A23="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B23&gt;0,1,0)))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="43" t="s">
+      <c r="F23" s="50" t="s">
         <v>329</v>
       </c>
-      <c r="G23" s="43"/>
+      <c r="G23" s="50"/>
       <c r="H23" s="30">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
@@ -9301,20 +9256,26 @@
       <c r="Y34" s="29"/>
     </row>
     <row r="35" spans="1:25" ht="14.4">
-      <c r="A35" s="39" t="s">
+      <c r="A35" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
       <c r="Y35" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="A35:H35"/>
@@ -9327,12 +9288,6 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="H15:H22">
     <cfRule type="dataBar" priority="1">

--- a/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
+++ b/templates/Consolidación Estados Financieros e Ingresos - Plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel-parser\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3C7F58-5614-4C23-88A9-2E3A12E77363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC51A81D-6752-4CA8-9B36-E17D2D77CFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="332">
   <si>
     <t>SALDOS INICIALES Y FINALES POR CUENTA</t>
   </si>
@@ -1032,9 +1032,6 @@
   </si>
   <si>
     <t>SALDO FINAL TOTAL</t>
-  </si>
-  <si>
-    <t>DINERO DISPONIBLE</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1047,7 @@
     <numFmt numFmtId="169" formatCode="\Q\ #,##0.00;[Red]\(\Q\ #,##0.00\);\-"/>
     <numFmt numFmtId="170" formatCode="\Q\ #,##0.00;[Red]\-\Q\ #,##0.00"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,22 +1151,8 @@
       <color theme="2" tint="-0.749961851863155"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF008080"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1237,12 +1220,6 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1284,7 +1261,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1366,16 +1343,22 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1395,18 +1378,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="13" fillId="10" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2314,20 +2285,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16.649999999999999" customHeight="1">
-      <c r="A1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="A1" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
     </row>
     <row r="2" spans="1:5" ht="17.850000000000001" customHeight="1">
-      <c r="A2" s="56" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
     </row>
     <row r="4" spans="1:5" ht="19.2" customHeight="1">
       <c r="A4" s="35" t="s">
@@ -7850,34 +7821,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="19.2" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
     </row>
     <row r="2" spans="1:11" ht="17.850000000000001" customHeight="1">
       <c r="A2" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="9" t="s">
@@ -7886,21 +7857,21 @@
       <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="55" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="42"/>
-      <c r="E3" s="57" t="s">
+      <c r="D3" s="40"/>
+      <c r="E3" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="42"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="57" t="s">
+      <c r="H3" s="55" t="s">
         <v>241</v>
       </c>
-      <c r="I3" s="42"/>
+      <c r="I3" s="40"/>
       <c r="J3" s="9"/>
       <c r="K3" s="9"/>
     </row>
@@ -8497,16 +8468,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.55" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
       <c r="X1" s="19" t="s">
         <v>290</v>
       </c>
@@ -8518,13 +8489,13 @@
       <c r="A2" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
       <c r="X2" s="19" t="s">
         <v>296</v>
       </c>
@@ -8568,22 +8539,22 @@
       </c>
     </row>
     <row r="5" spans="1:25" ht="26.4" customHeight="1">
-      <c r="A5" s="52">
+      <c r="A5" s="42">
         <v>46235</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="52">
+      <c r="B5" s="40"/>
+      <c r="C5" s="42">
         <v>46253</v>
       </c>
-      <c r="D5" s="42"/>
-      <c r="E5" s="53" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="54" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="44" t="s">
         <v>303</v>
       </c>
-      <c r="H5" s="42"/>
+      <c r="H5" s="40"/>
       <c r="X5" s="19" t="s">
         <v>304</v>
       </c>
@@ -8618,58 +8589,49 @@
         <v>292</v>
       </c>
       <c r="H7" s="9"/>
-      <c r="I7" s="48" t="s">
+      <c r="I7" s="50" t="s">
         <v>331</v>
       </c>
-      <c r="J7" s="48"/>
-      <c r="K7" s="39" t="s">
-        <v>332</v>
-      </c>
-      <c r="L7" s="39"/>
-      <c r="X7" s="19" t="s">
+      <c r="J7" s="50"/>
+      <c r="V7" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="Y7" s="33">
-        <f t="shared" si="0"/>
+      <c r="W7" s="33">
+        <f>B20</f>
         <v>622.82000000000005</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="16.2" customHeight="1">
-      <c r="A8" s="43">
+      <c r="A8" s="45">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="43">
+      <c r="B8" s="46"/>
+      <c r="C8" s="45">
         <f>IFERROR(AVERAGEIF(H15:H22,"&gt;0"),0)</f>
         <v>12860.23625</v>
       </c>
-      <c r="D8" s="44"/>
-      <c r="E8" s="43">
+      <c r="D8" s="46"/>
+      <c r="E8" s="45">
         <f>IFERROR(MAX(H15:H22),0)</f>
         <v>32704.7</v>
       </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="45">
+      <c r="F8" s="46"/>
+      <c r="G8" s="47">
         <f>COUNTIF(H15:H22,"&gt;0")</f>
         <v>8</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="49">
+      <c r="H8" s="48"/>
+      <c r="I8" s="51">
         <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$D$5:$D$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$D$5:$D$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$D$5:$D$200),0)))</f>
         <v>268945.52</v>
       </c>
-      <c r="J8" s="49"/>
-      <c r="K8" s="40">
-        <f>IF($E$5&lt;&gt;"TODAS",IFERROR(SUMIF('SALDOS POR CUENTA'!$B$5:$B$200,$E$5,'SALDOS POR CUENTA'!$E$13:$E$200),0),IF($G$5&lt;&gt;"TODOS",IFERROR(SUMIF('SALDOS POR CUENTA'!$A$5:$A$200,$G$5,'SALDOS POR CUENTA'!$E$13:$E$200),0),IFERROR(SUM('SALDOS POR CUENTA'!$E$13:$E$200),0)))</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="40"/>
-      <c r="X8" s="19" t="s">
+      <c r="J8" s="51"/>
+      <c r="V8" s="19" t="s">
         <v>310</v>
       </c>
-      <c r="Y8" s="33">
-        <f t="shared" si="0"/>
+      <c r="W8" s="33">
+        <f>B21</f>
         <v>2766.44</v>
       </c>
     </row>
@@ -8718,17 +8680,17 @@
       </c>
     </row>
     <row r="13" spans="1:25" ht="9.6" customHeight="1">
-      <c r="A13" s="47" t="s">
+      <c r="A13" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="F13" s="47" t="s">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="F13" s="49" t="s">
         <v>316</v>
       </c>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="40"/>
       <c r="X13" s="19" t="s">
         <v>317</v>
       </c>
@@ -9052,10 +9014,10 @@
         <f>IF(A23="",0,IF($G$5="TODOS",IFERROR(INDEX('REPORTE CREDITOS DIARIOS'!$K$5:$K$23,MATCH(A23,'REPORTE CREDITOS DIARIOS'!$A$5:$A$23,0)),0),IF(B23&gt;0,1,0)))</f>
         <v>0</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="52" t="s">
         <v>329</v>
       </c>
-      <c r="G23" s="50"/>
+      <c r="G23" s="52"/>
       <c r="H23" s="30">
         <f>SUM(H15:H22)</f>
         <v>102881.89</v>
@@ -9259,25 +9221,17 @@
       <c r="A35" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="B35" s="42"/>
-      <c r="C35" s="42"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+      <c r="H35" s="40"/>
       <c r="Y35" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="K8:L8"/>
+  <mergeCells count="16">
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:D8"/>
@@ -9288,6 +9242,12 @@
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="H15:H22">
     <cfRule type="dataBar" priority="1">
